--- a/willitboard_operadores.xlsx
+++ b/willitboard_operadores.xlsx
@@ -2019,33 +2019,73 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="8" t="n"/>
-      <c r="L10" s="8" t="n"/>
-      <c r="M10" s="8" t="n"/>
-      <c r="N10" s="8" t="n"/>
-      <c r="O10" s="8" t="n"/>
-      <c r="P10" s="8" t="n"/>
-      <c r="Q10" s="8" t="n"/>
-      <c r="R10" s="8" t="n"/>
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>stena-line</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>Stena Line</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>ferry</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E10" s="33" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>descriptivo</t>
+        </is>
+      </c>
+      <c r="G10" s="33" t="n"/>
+      <c r="H10" s="33" t="n"/>
+      <c r="I10" s="33" t="n"/>
+      <c r="J10" s="33" t="n"/>
+      <c r="K10" s="33" t="n"/>
+      <c r="L10" s="33" t="n"/>
+      <c r="M10" s="33" t="n"/>
+      <c r="N10" s="33" t="n"/>
+      <c r="O10" s="33" t="n"/>
+      <c r="P10" s="33" t="n"/>
+      <c r="Q10" s="33" t="n"/>
+      <c r="R10" s="33" t="n"/>
       <c r="S10" s="33" t="n"/>
-      <c r="T10" s="8" t="n"/>
-      <c r="U10" s="8" t="n"/>
-      <c r="V10" s="8" t="n"/>
-      <c r="W10" s="8" t="n"/>
-      <c r="X10" s="8" t="n"/>
-      <c r="Y10" s="8" t="n"/>
-      <c r="Z10" s="9" t="n"/>
-      <c r="AA10" s="35" t="n"/>
+      <c r="T10" s="33" t="n"/>
+      <c r="U10" s="33" t="n"/>
+      <c r="V10" s="33" t="n"/>
+      <c r="W10" s="33" t="n"/>
+      <c r="X10" s="33" t="inlineStr">
+        <is>
+          <t>If you are travelling by car there is no limit to the amount of luggage you can carry in your vehicle as it will remain in your vehicle on our car deck. For foot passengers travelling to Sweden, Denmark, Germany, Latvia and Poland, there is no limit on the amount of luggage you can bring with you, however you need to be able to carry it onboard yourself. For foot passengers travelling to Ireland and to the UK from Ireland, there is no limit to the amount of luggage you can bring with you, however, hand luggage must be no larger than 60cm x 50cm x 40cm and you must be able to carry it yourself. If you are travelling with luggage that is larger than this it must be checked-in prior to boarding. Your luggage will be safely stowed during the sailing and can be collected upon arrival in the terminal. You will not be able to access your luggage during the sailing so please ensure you remove all necessary items before checking it in. If you are travelling by foot or by Rail &amp; Sail on our Harwich-Hook of Holland route, you may take as much luggage as you like, as long as you can carry it onboard yourself. Passengers travelling on a day trip on our Irish Sea routes may carry one piece of small hand luggage. Any additional pieces of luggage will be charged at our discretion.</t>
+        </is>
+      </c>
+      <c r="Y10" s="33" t="inlineStr">
+        <is>
+          <t>Verificado por Marcos el 23/09/2026: pegó el texto completo de la página oficial y confirmó los cuatro puntos pedidos. PRIMER FERRY DEL DATASET. limit_type = descriptivo A PROPÓSITO, mismo criterio que Eurostar: la única medida publicada, 60 x 50 x 40 cm, aplica SOLO a pasajeros a pie hacia Irlanda y hacia el Reino Unido desde Irlanda. En las rutas a Suecia, Dinamarca, Alemania, Letonia y Polonia no hay límite de tamaño, y en Harwich-Hook of Holland tampoco. Cargar 60x50x40 en la terna de cabina la aplicaría a todas las rutas y sería falso en la mayoría. Por eso la cifra vive dentro de la regla, acotada a sus rutas. Sin ningún peso en kg publicado (confirmado). La regla es TEXTUAL: frases copiadas de la página, sin parafrasear. EXCLUIDO a propósito: el párrafo final sobre productos restringidos entre el Reino Unido y la UE, porque es una regla aduanera y no de tamaño de equipaje. FUENTE: el mismo texto figura en stenaline.co.uk y en stenalinetravel.com; se cita .co.uk por ser el sitio del propio operador. pais = SE por Stena Line AB (Gotemburgo).</t>
+        </is>
+      </c>
+      <c r="Z10" s="36" t="inlineStr">
+        <is>
+          <t>https://www.stenaline.co.uk/customer-service/pre-travel/how-much-luggage-can-i-bring-with-me</t>
+        </is>
+      </c>
+      <c r="AA10" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n"/>

--- a/willitboard_operadores.xlsx
+++ b/willitboard_operadores.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1119,6 +1119,18 @@
       <c r="B52" s="21" t="inlineStr">
         <is>
           <t>https://www.trenitalia.com/en/information/faqs-section.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="inlineStr">
+        <is>
+          <t>tarifa_referencia (esquema 1.4, 24/09/2026)</t>
+        </is>
+      </c>
+      <c r="B53" s="21" t="inlineStr">
+        <is>
+          <t>Columna AB, opcional, solo para aerolíneas con límite dimensional. Nombre de la tarifa a la que corresponden las cifras, copiado tal como lo escribe el operador en su página oficial (por ejemplo "Basic"). No se traduce. Vacía significa "no confirmada": la ficha muestra entonces el aviso genérico de tarifas. Se completa solo después de que Marcos confirma el nombre en la fuente, igual que cualquier otro dato.</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA120"/>
+  <dimension ref="A1:AB120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1163,6 +1175,7 @@
     <col width="49" customWidth="1" min="25" max="25"/>
     <col width="46" customWidth="1" min="26" max="26"/>
     <col width="21" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1301,6 +1314,11 @@
           <t>verificado_el</t>
         </is>
       </c>
+      <c r="AB1" s="17" t="inlineStr">
+        <is>
+          <t>tarifa_referencia</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
@@ -1436,6 +1454,11 @@
       <c r="AA2" s="6" t="inlineStr">
         <is>
           <t>AAAA-MM-DD</t>
+        </is>
+      </c>
+      <c r="AB2" s="6" t="inlineStr">
+        <is>
+          <t>nombre de la tarifa tal como lo escribe el operador; solo aerolíneas</t>
         </is>
       </c>
     </row>
@@ -1527,6 +1550,7 @@
       <c r="AA3" s="32" t="n">
         <v>46277</v>
       </c>
+      <c r="AB3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -1624,6 +1648,7 @@
       <c r="AA4" s="34" t="n">
         <v>46277</v>
       </c>
+      <c r="AB4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -1721,6 +1746,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
+      <c r="AB5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="33" t="inlineStr">
@@ -1790,6 +1816,7 @@
           <t>2026-09-13</t>
         </is>
       </c>
+      <c r="AB6" s="33" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="33" t="inlineStr">
@@ -1859,6 +1886,7 @@
           <t>2026-09-13</t>
         </is>
       </c>
+      <c r="AB7" s="33" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="33" t="inlineStr">
@@ -1928,6 +1956,7 @@
           <t>2026-09-13</t>
         </is>
       </c>
+      <c r="AB8" s="33" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -2017,6 +2046,7 @@
           <t>2026-09-17</t>
         </is>
       </c>
+      <c r="AB9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="33" t="inlineStr">
@@ -2086,25 +2116,72 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="AB10" s="33" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n"/>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="8" t="n"/>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>vueling</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Vueling</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>20</v>
+      </c>
       <c r="K11" s="8" t="n"/>
-      <c r="L11" s="8" t="n"/>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="M11" s="8" t="n"/>
-      <c r="N11" s="8" t="n"/>
-      <c r="O11" s="8" t="n"/>
-      <c r="P11" s="8" t="n"/>
-      <c r="Q11" s="8" t="n"/>
+      <c r="N11" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>10</v>
+      </c>
       <c r="R11" s="8" t="n"/>
       <c r="S11" s="33" t="n"/>
       <c r="T11" s="8" t="n"/>
@@ -2112,28 +2189,91 @@
       <c r="V11" s="8" t="n"/>
       <c r="W11" s="8" t="n"/>
       <c r="X11" s="8" t="n"/>
-      <c r="Y11" s="8" t="n"/>
-      <c r="Z11" s="9" t="n"/>
+      <c r="Y11" s="8" t="inlineStr">
+        <is>
+          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. Bolso bajo el asiento 40x30x20 cm en todas las tarifas, sin peso publicado. Valija de compartimento 55x40x20 cm y 10 kg: incluida en Fly/Fly Grande/Fly Pro/Premium, de pago en Fly Light. [NO SÉ] nombre exacto del extra (cabina_addon vacío) y si las medidas incluyen ruedas y asas. Confirmar además el nombre de la tarifa base.</t>
+        </is>
+      </c>
+      <c r="Z11" s="9" t="inlineStr">
+        <is>
+          <t>https://help.vueling.com/hc/en-gb/articles/19798835176081-Hand-Luggage-Allowance-Cabin-bags-allowance</t>
+        </is>
+      </c>
       <c r="AA11" s="35" t="n"/>
+      <c r="AB11" s="8" t="inlineStr">
+        <is>
+          <t>Fly Light</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>lufthansa</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Lufthansa</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="K12" s="8" t="n"/>
-      <c r="L12" s="8" t="n"/>
-      <c r="M12" s="8" t="n"/>
-      <c r="N12" s="8" t="n"/>
-      <c r="O12" s="8" t="n"/>
-      <c r="P12" s="8" t="n"/>
-      <c r="Q12" s="8" t="n"/>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>Carry-on bag (online only)</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>8</v>
+      </c>
       <c r="R12" s="8" t="n"/>
       <c r="S12" s="33" t="n"/>
       <c r="T12" s="8" t="n"/>
@@ -2141,28 +2281,87 @@
       <c r="V12" s="8" t="n"/>
       <c r="W12" s="8" t="n"/>
       <c r="X12" s="8" t="n"/>
-      <c r="Y12" s="8" t="n"/>
-      <c r="Z12" s="9" t="n"/>
+      <c r="Y12" s="8" t="inlineStr">
+        <is>
+          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. Economy Basic incluye solo el artículo personal 40x30x15 cm; el equipaje de mano 55x40x23 cm y 8 kg no está incluido y se compra solo online, hasta 2 h antes. Economy Light, Comfort, Comfort Green y Flex lo incluyen. [NO SÉ] peso del artículo personal y si las medidas incluyen ruedas y asas. cabina_addon es descripción del asistente, no nombre comercial: confirmar cómo lo llama Lufthansa. La URL es la versión /ba/en/ que devolvió la búsqueda; si existe la misma página en /de/en/, citar esa.</t>
+        </is>
+      </c>
+      <c r="Z12" s="9" t="inlineStr">
+        <is>
+          <t>https://www.lufthansa.com/ba/en/prepare-for-your-trip/travel-classes/economy-basic</t>
+        </is>
+      </c>
       <c r="AA12" s="35" t="n"/>
+      <c r="AB12" s="8" t="inlineStr">
+        <is>
+          <t>Economy Basic</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n"/>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="8" t="n"/>
-      <c r="J13" s="8" t="n"/>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>sas</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="K13" s="8" t="n"/>
-      <c r="L13" s="8" t="n"/>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="M13" s="8" t="n"/>
-      <c r="N13" s="8" t="n"/>
-      <c r="O13" s="8" t="n"/>
-      <c r="P13" s="8" t="n"/>
-      <c r="Q13" s="8" t="n"/>
+      <c r="N13" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="P13" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>8</v>
+      </c>
       <c r="R13" s="8" t="n"/>
       <c r="S13" s="33" t="n"/>
       <c r="T13" s="8" t="n"/>
@@ -2170,27 +2369,90 @@
       <c r="V13" s="8" t="n"/>
       <c r="W13" s="8" t="n"/>
       <c r="X13" s="8" t="n"/>
-      <c r="Y13" s="8" t="n"/>
-      <c r="Z13" s="9" t="n"/>
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. Artículo personal 40x30x15 cm y capacidad máxima 18 L (dato que el esquema no guarda). Equipaje de cabina 55x40x23 cm, 8 kg: incluido en Economy Standard, Flex, Premium y Business; en Economy Light se puede comprar. [NO SÉ] peso del artículo personal, nombre del extra y ruedas/asas. Confirmar si la tarifa base hoy se llama Economy Light o SAS Go Light. pais = SE por SAS AB (Estocolmo).</t>
+        </is>
+      </c>
+      <c r="Z13" s="9" t="inlineStr">
+        <is>
+          <t>https://www.flysas.com/us-en/travel-info/baggage/carry-on</t>
+        </is>
+      </c>
       <c r="AA13" s="35" t="n"/>
+      <c r="AB13" s="8" t="inlineStr">
+        <is>
+          <t>Economy Light</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n"/>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n"/>
-      <c r="K14" s="8" t="n"/>
-      <c r="L14" s="8" t="n"/>
-      <c r="M14" s="8" t="n"/>
-      <c r="N14" s="8" t="n"/>
-      <c r="O14" s="8" t="n"/>
-      <c r="P14" s="8" t="n"/>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>norwegian</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Norwegian</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>LowFare+</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>23</v>
+      </c>
       <c r="Q14" s="8" t="n"/>
       <c r="R14" s="8" t="n"/>
       <c r="S14" s="33" t="n"/>
@@ -2199,115 +2461,357 @@
       <c r="V14" s="8" t="n"/>
       <c r="W14" s="8" t="n"/>
       <c r="X14" s="8" t="n"/>
-      <c r="Y14" s="8" t="n"/>
-      <c r="Z14" s="9" t="n"/>
+      <c r="Y14" s="8" t="inlineStr">
+        <is>
+          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. BLOQUEADA POR ESQUEMA: LowFare incluye solo el bolso bajo el asiento (30x40x20 cm, máx. 10 kg). LowFare+ suma la valija 55x40x23 cm con PESO COMBINADO de 10 kg para los dos bultos; Flex, 15 kg combinados. El esquema guarda peso por bulto: dejar cabina_kg vacío haría que la ficha diga "sin límite de peso publicado", que es falso. No publicar hasta decidir cómo se modela el peso combinado. [NO SÉ] ruedas/asas.</t>
+        </is>
+      </c>
+      <c r="Z14" s="9" t="inlineStr">
+        <is>
+          <t>https://www.norwegian.com/us/travel-info/baggage/hand-baggage/</t>
+        </is>
+      </c>
       <c r="AA14" s="35" t="n"/>
+      <c r="AB14" s="8" t="inlineStr">
+        <is>
+          <t>LowFare</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="8" t="n"/>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>air-france</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Air France</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="K15" s="8" t="n"/>
-      <c r="L15" s="8" t="n"/>
-      <c r="M15" s="8" t="n"/>
-      <c r="N15" s="8" t="n"/>
-      <c r="O15" s="8" t="n"/>
-      <c r="P15" s="8" t="n"/>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>Hand Baggage option</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="P15" s="8" t="n">
+        <v>25</v>
+      </c>
       <c r="Q15" s="8" t="n"/>
-      <c r="R15" s="8" t="n"/>
+      <c r="R15" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="S15" s="33" t="n"/>
       <c r="T15" s="8" t="n"/>
       <c r="U15" s="8" t="n"/>
       <c r="V15" s="8" t="n"/>
       <c r="W15" s="8" t="n"/>
       <c r="X15" s="8" t="n"/>
-      <c r="Y15" s="8" t="n"/>
-      <c r="Z15" s="9" t="n"/>
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. BLOQUEADA POR ESQUEMA: en Economy el peso es COMBINADO, 12 kg entre la valija y el bolso pequeño. Bolso pequeño 40x30x15 cm; valija 55x35x25 cm "including pockets, wheels, and handles". Las tarifas Basic incluyen solo el bolso pequeño; la valija requiere Flying Blue Gold+ o comprar la opción. Confirmar el nombre exacto de la tarifa (Basic o Light) y del extra.</t>
+        </is>
+      </c>
+      <c r="Z15" s="9" t="inlineStr">
+        <is>
+          <t>https://wwws.airfrance.fr/en/information/bagages/bagage-cabine-soute</t>
+        </is>
+      </c>
       <c r="AA15" s="35" t="n"/>
+      <c r="AB15" s="8" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>klm</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="K16" s="8" t="n"/>
-      <c r="L16" s="8" t="n"/>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="M16" s="8" t="n"/>
-      <c r="N16" s="8" t="n"/>
-      <c r="O16" s="8" t="n"/>
-      <c r="P16" s="8" t="n"/>
+      <c r="N16" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="P16" s="8" t="n">
+        <v>25</v>
+      </c>
       <c r="Q16" s="8" t="n"/>
-      <c r="R16" s="8" t="n"/>
+      <c r="R16" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="S16" s="33" t="n"/>
       <c r="T16" s="8" t="n"/>
       <c r="U16" s="8" t="n"/>
       <c r="V16" s="8" t="n"/>
       <c r="W16" s="8" t="n"/>
       <c r="X16" s="8" t="n"/>
-      <c r="Y16" s="8" t="n"/>
-      <c r="Z16" s="9" t="n"/>
+      <c r="Y16" s="8" t="inlineStr">
+        <is>
+          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. BLOQUEADA POR ESQUEMA: peso COMBINADO de 12 kg entre bolso pequeño y valija en Economy. Bolso pequeño 40x30x15 cm bajo el asiento; valija 55x35x25 cm "including handles and wheels". Economy Light, Standard y Flex incluyen la valija; Basic solo el bolso pequeño. [NO SÉ] nombre del extra.</t>
+        </is>
+      </c>
+      <c r="Z16" s="9" t="inlineStr">
+        <is>
+          <t>https://www.klm.nl/en/information/baggage/hand-baggage-allowance</t>
+        </is>
+      </c>
       <c r="AA16" s="35" t="n"/>
+      <c r="AB16" s="8" t="inlineStr">
+        <is>
+          <t>Economy Basic</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n"/>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="8" t="n"/>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>transavia</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Transavia</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>20</v>
+      </c>
       <c r="K17" s="8" t="n"/>
-      <c r="L17" s="8" t="n"/>
-      <c r="M17" s="8" t="n"/>
-      <c r="N17" s="8" t="n"/>
-      <c r="O17" s="8" t="n"/>
-      <c r="P17" s="8" t="n"/>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>Smart fare, or cabin bag bought separately</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="P17" s="8" t="n">
+        <v>25</v>
+      </c>
       <c r="Q17" s="8" t="n"/>
-      <c r="R17" s="8" t="n"/>
+      <c r="R17" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="S17" s="33" t="n"/>
       <c r="T17" s="8" t="n"/>
       <c r="U17" s="8" t="n"/>
       <c r="V17" s="8" t="n"/>
       <c r="W17" s="8" t="n"/>
       <c r="X17" s="8" t="n"/>
-      <c r="Y17" s="8" t="n"/>
-      <c r="Z17" s="9" t="n"/>
+      <c r="Y17" s="8" t="inlineStr">
+        <is>
+          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. BLOQUEADA POR ESQUEMA: bolso pequeño 40x30x20 cm y hasta 10 kg; con valija 55x40x25 cm el PESO ES COMBINADO, 10 kg entre los dos. Medidas "including wheels and handles". Basic y Plus no incluyen la valija; Smart y Max sí, con Priority Boarding. cabina_addon es descripción del asistente: confirmar el nombre comercial.</t>
+        </is>
+      </c>
+      <c r="Z17" s="9" t="inlineStr">
+        <is>
+          <t>https://www.transavia.com/help/en-eu/baggage/cabin-baggage/how-much-to-bring</t>
+        </is>
+      </c>
       <c r="AA17" s="35" t="n"/>
+      <c r="AB17" s="8" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>iberia</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Iberia</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
       <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
+      <c r="H18" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="K18" s="8" t="n"/>
       <c r="L18" s="8" t="n"/>
       <c r="M18" s="8" t="n"/>
-      <c r="N18" s="8" t="n"/>
-      <c r="O18" s="8" t="n"/>
-      <c r="P18" s="8" t="n"/>
-      <c r="Q18" s="8" t="n"/>
+      <c r="N18" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>10</v>
+      </c>
       <c r="R18" s="8" t="n"/>
       <c r="S18" s="33" t="n"/>
       <c r="T18" s="8" t="n"/>
@@ -2315,9 +2819,18 @@
       <c r="V18" s="8" t="n"/>
       <c r="W18" s="8" t="n"/>
       <c r="X18" s="8" t="n"/>
-      <c r="Y18" s="8" t="n"/>
-      <c r="Z18" s="9" t="n"/>
+      <c r="Y18" s="8" t="inlineStr">
+        <is>
+          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. FUENTE DÉBIL: iberia.com devolvió error (redirecciones y 404) y las cifras salen del portal de AGENCIAS de Iberia: equipaje de mano 56x40x25 cm y 10 kg en Economy, artículo personal 30x40x15 cm. Hace falta la página pública de iberia.com para publicar. [NO SÉ] si la tarifa Basic incluye la valija (personal_incluido y cabina_incluida vacíos a propósito), peso del artículo personal y ruedas/asas.</t>
+        </is>
+      </c>
+      <c r="Z18" s="9" t="inlineStr">
+        <is>
+          <t>https://agencias.iberia.com/content/iberia-agencias/language-masters/en/informacion-viaje/equipajes/hand-baggage.html</t>
+        </is>
+      </c>
       <c r="AA18" s="35" t="n"/>
+      <c r="AB18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n"/>
@@ -2347,6 +2860,7 @@
       <c r="Y19" s="8" t="n"/>
       <c r="Z19" s="9" t="n"/>
       <c r="AA19" s="35" t="n"/>
+      <c r="AB19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n"/>
@@ -2376,6 +2890,7 @@
       <c r="Y20" s="8" t="n"/>
       <c r="Z20" s="9" t="n"/>
       <c r="AA20" s="35" t="n"/>
+      <c r="AB20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n"/>
@@ -2405,6 +2920,7 @@
       <c r="Y21" s="8" t="n"/>
       <c r="Z21" s="9" t="n"/>
       <c r="AA21" s="35" t="n"/>
+      <c r="AB21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n"/>
@@ -2434,6 +2950,7 @@
       <c r="Y22" s="8" t="n"/>
       <c r="Z22" s="9" t="n"/>
       <c r="AA22" s="35" t="n"/>
+      <c r="AB22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n"/>
@@ -2463,6 +2980,7 @@
       <c r="Y23" s="8" t="n"/>
       <c r="Z23" s="9" t="n"/>
       <c r="AA23" s="35" t="n"/>
+      <c r="AB23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n"/>
@@ -2492,6 +3010,7 @@
       <c r="Y24" s="8" t="n"/>
       <c r="Z24" s="9" t="n"/>
       <c r="AA24" s="35" t="n"/>
+      <c r="AB24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n"/>
@@ -2521,6 +3040,7 @@
       <c r="Y25" s="8" t="n"/>
       <c r="Z25" s="9" t="n"/>
       <c r="AA25" s="35" t="n"/>
+      <c r="AB25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n"/>
@@ -2550,6 +3070,7 @@
       <c r="Y26" s="8" t="n"/>
       <c r="Z26" s="9" t="n"/>
       <c r="AA26" s="35" t="n"/>
+      <c r="AB26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n"/>
@@ -2579,6 +3100,7 @@
       <c r="Y27" s="8" t="n"/>
       <c r="Z27" s="9" t="n"/>
       <c r="AA27" s="35" t="n"/>
+      <c r="AB27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n"/>
@@ -2608,6 +3130,7 @@
       <c r="Y28" s="8" t="n"/>
       <c r="Z28" s="9" t="n"/>
       <c r="AA28" s="35" t="n"/>
+      <c r="AB28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n"/>
@@ -2637,6 +3160,7 @@
       <c r="Y29" s="8" t="n"/>
       <c r="Z29" s="9" t="n"/>
       <c r="AA29" s="35" t="n"/>
+      <c r="AB29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n"/>
@@ -2666,6 +3190,7 @@
       <c r="Y30" s="8" t="n"/>
       <c r="Z30" s="9" t="n"/>
       <c r="AA30" s="35" t="n"/>
+      <c r="AB30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
@@ -2695,6 +3220,7 @@
       <c r="Y31" s="8" t="n"/>
       <c r="Z31" s="9" t="n"/>
       <c r="AA31" s="35" t="n"/>
+      <c r="AB31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n"/>
@@ -2724,6 +3250,7 @@
       <c r="Y32" s="8" t="n"/>
       <c r="Z32" s="9" t="n"/>
       <c r="AA32" s="35" t="n"/>
+      <c r="AB32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
@@ -2753,6 +3280,7 @@
       <c r="Y33" s="8" t="n"/>
       <c r="Z33" s="9" t="n"/>
       <c r="AA33" s="35" t="n"/>
+      <c r="AB33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n"/>
@@ -2782,6 +3310,7 @@
       <c r="Y34" s="8" t="n"/>
       <c r="Z34" s="9" t="n"/>
       <c r="AA34" s="35" t="n"/>
+      <c r="AB34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
@@ -2811,6 +3340,7 @@
       <c r="Y35" s="8" t="n"/>
       <c r="Z35" s="9" t="n"/>
       <c r="AA35" s="35" t="n"/>
+      <c r="AB35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n"/>
@@ -2840,6 +3370,7 @@
       <c r="Y36" s="8" t="n"/>
       <c r="Z36" s="9" t="n"/>
       <c r="AA36" s="35" t="n"/>
+      <c r="AB36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
@@ -2869,6 +3400,7 @@
       <c r="Y37" s="8" t="n"/>
       <c r="Z37" s="9" t="n"/>
       <c r="AA37" s="35" t="n"/>
+      <c r="AB37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n"/>
@@ -2898,6 +3430,7 @@
       <c r="Y38" s="8" t="n"/>
       <c r="Z38" s="9" t="n"/>
       <c r="AA38" s="35" t="n"/>
+      <c r="AB38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
@@ -2927,6 +3460,7 @@
       <c r="Y39" s="8" t="n"/>
       <c r="Z39" s="9" t="n"/>
       <c r="AA39" s="35" t="n"/>
+      <c r="AB39" s="8" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n"/>
@@ -2956,6 +3490,7 @@
       <c r="Y40" s="8" t="n"/>
       <c r="Z40" s="9" t="n"/>
       <c r="AA40" s="35" t="n"/>
+      <c r="AB40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
@@ -2985,6 +3520,7 @@
       <c r="Y41" s="8" t="n"/>
       <c r="Z41" s="9" t="n"/>
       <c r="AA41" s="35" t="n"/>
+      <c r="AB41" s="8" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n"/>
@@ -3014,6 +3550,7 @@
       <c r="Y42" s="8" t="n"/>
       <c r="Z42" s="9" t="n"/>
       <c r="AA42" s="35" t="n"/>
+      <c r="AB42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n"/>
@@ -3043,6 +3580,7 @@
       <c r="Y43" s="8" t="n"/>
       <c r="Z43" s="9" t="n"/>
       <c r="AA43" s="35" t="n"/>
+      <c r="AB43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n"/>
@@ -3072,6 +3610,7 @@
       <c r="Y44" s="8" t="n"/>
       <c r="Z44" s="9" t="n"/>
       <c r="AA44" s="35" t="n"/>
+      <c r="AB44" s="8" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n"/>
@@ -3101,6 +3640,7 @@
       <c r="Y45" s="8" t="n"/>
       <c r="Z45" s="9" t="n"/>
       <c r="AA45" s="35" t="n"/>
+      <c r="AB45" s="8" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n"/>
@@ -3130,6 +3670,7 @@
       <c r="Y46" s="8" t="n"/>
       <c r="Z46" s="9" t="n"/>
       <c r="AA46" s="35" t="n"/>
+      <c r="AB46" s="8" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n"/>
@@ -3159,6 +3700,7 @@
       <c r="Y47" s="8" t="n"/>
       <c r="Z47" s="9" t="n"/>
       <c r="AA47" s="35" t="n"/>
+      <c r="AB47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n"/>
@@ -3188,6 +3730,7 @@
       <c r="Y48" s="8" t="n"/>
       <c r="Z48" s="9" t="n"/>
       <c r="AA48" s="35" t="n"/>
+      <c r="AB48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
@@ -3217,6 +3760,7 @@
       <c r="Y49" s="8" t="n"/>
       <c r="Z49" s="9" t="n"/>
       <c r="AA49" s="35" t="n"/>
+      <c r="AB49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n"/>
@@ -3246,6 +3790,7 @@
       <c r="Y50" s="8" t="n"/>
       <c r="Z50" s="9" t="n"/>
       <c r="AA50" s="35" t="n"/>
+      <c r="AB50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n"/>
@@ -3275,6 +3820,7 @@
       <c r="Y51" s="8" t="n"/>
       <c r="Z51" s="9" t="n"/>
       <c r="AA51" s="35" t="n"/>
+      <c r="AB51" s="8" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n"/>
@@ -3304,6 +3850,7 @@
       <c r="Y52" s="8" t="n"/>
       <c r="Z52" s="9" t="n"/>
       <c r="AA52" s="35" t="n"/>
+      <c r="AB52" s="8" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
@@ -3333,6 +3880,7 @@
       <c r="Y53" s="8" t="n"/>
       <c r="Z53" s="9" t="n"/>
       <c r="AA53" s="35" t="n"/>
+      <c r="AB53" s="8" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n"/>
@@ -3362,6 +3910,7 @@
       <c r="Y54" s="8" t="n"/>
       <c r="Z54" s="9" t="n"/>
       <c r="AA54" s="35" t="n"/>
+      <c r="AB54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
@@ -3391,6 +3940,7 @@
       <c r="Y55" s="8" t="n"/>
       <c r="Z55" s="9" t="n"/>
       <c r="AA55" s="35" t="n"/>
+      <c r="AB55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n"/>
@@ -3420,6 +3970,7 @@
       <c r="Y56" s="8" t="n"/>
       <c r="Z56" s="9" t="n"/>
       <c r="AA56" s="35" t="n"/>
+      <c r="AB56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
@@ -3449,6 +4000,7 @@
       <c r="Y57" s="8" t="n"/>
       <c r="Z57" s="9" t="n"/>
       <c r="AA57" s="35" t="n"/>
+      <c r="AB57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n"/>
@@ -3478,6 +4030,7 @@
       <c r="Y58" s="8" t="n"/>
       <c r="Z58" s="9" t="n"/>
       <c r="AA58" s="35" t="n"/>
+      <c r="AB58" s="8" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
@@ -3507,6 +4060,7 @@
       <c r="Y59" s="8" t="n"/>
       <c r="Z59" s="9" t="n"/>
       <c r="AA59" s="35" t="n"/>
+      <c r="AB59" s="8" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n"/>
@@ -3536,6 +4090,7 @@
       <c r="Y60" s="8" t="n"/>
       <c r="Z60" s="9" t="n"/>
       <c r="AA60" s="35" t="n"/>
+      <c r="AB60" s="8" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
@@ -3565,6 +4120,7 @@
       <c r="Y61" s="8" t="n"/>
       <c r="Z61" s="9" t="n"/>
       <c r="AA61" s="35" t="n"/>
+      <c r="AB61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n"/>
@@ -3594,6 +4150,7 @@
       <c r="Y62" s="8" t="n"/>
       <c r="Z62" s="9" t="n"/>
       <c r="AA62" s="35" t="n"/>
+      <c r="AB62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n"/>
@@ -3623,6 +4180,7 @@
       <c r="Y63" s="8" t="n"/>
       <c r="Z63" s="9" t="n"/>
       <c r="AA63" s="35" t="n"/>
+      <c r="AB63" s="8" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n"/>
@@ -3652,6 +4210,7 @@
       <c r="Y64" s="8" t="n"/>
       <c r="Z64" s="9" t="n"/>
       <c r="AA64" s="35" t="n"/>
+      <c r="AB64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n"/>
@@ -3681,6 +4240,7 @@
       <c r="Y65" s="8" t="n"/>
       <c r="Z65" s="9" t="n"/>
       <c r="AA65" s="35" t="n"/>
+      <c r="AB65" s="8" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n"/>
@@ -3710,6 +4270,7 @@
       <c r="Y66" s="8" t="n"/>
       <c r="Z66" s="9" t="n"/>
       <c r="AA66" s="35" t="n"/>
+      <c r="AB66" s="8" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n"/>
@@ -3739,6 +4300,7 @@
       <c r="Y67" s="8" t="n"/>
       <c r="Z67" s="9" t="n"/>
       <c r="AA67" s="35" t="n"/>
+      <c r="AB67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n"/>
@@ -3768,6 +4330,7 @@
       <c r="Y68" s="8" t="n"/>
       <c r="Z68" s="9" t="n"/>
       <c r="AA68" s="35" t="n"/>
+      <c r="AB68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
@@ -3797,6 +4360,7 @@
       <c r="Y69" s="8" t="n"/>
       <c r="Z69" s="9" t="n"/>
       <c r="AA69" s="35" t="n"/>
+      <c r="AB69" s="8" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n"/>
@@ -3826,6 +4390,7 @@
       <c r="Y70" s="8" t="n"/>
       <c r="Z70" s="9" t="n"/>
       <c r="AA70" s="35" t="n"/>
+      <c r="AB70" s="8" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
@@ -3855,6 +4420,7 @@
       <c r="Y71" s="8" t="n"/>
       <c r="Z71" s="9" t="n"/>
       <c r="AA71" s="35" t="n"/>
+      <c r="AB71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n"/>
@@ -3884,6 +4450,7 @@
       <c r="Y72" s="8" t="n"/>
       <c r="Z72" s="9" t="n"/>
       <c r="AA72" s="35" t="n"/>
+      <c r="AB72" s="8" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
@@ -3913,6 +4480,7 @@
       <c r="Y73" s="8" t="n"/>
       <c r="Z73" s="9" t="n"/>
       <c r="AA73" s="35" t="n"/>
+      <c r="AB73" s="8" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n"/>
@@ -3942,6 +4510,7 @@
       <c r="Y74" s="8" t="n"/>
       <c r="Z74" s="9" t="n"/>
       <c r="AA74" s="35" t="n"/>
+      <c r="AB74" s="8" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n"/>
@@ -3971,6 +4540,7 @@
       <c r="Y75" s="8" t="n"/>
       <c r="Z75" s="9" t="n"/>
       <c r="AA75" s="35" t="n"/>
+      <c r="AB75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="n"/>
@@ -4000,6 +4570,7 @@
       <c r="Y76" s="8" t="n"/>
       <c r="Z76" s="9" t="n"/>
       <c r="AA76" s="35" t="n"/>
+      <c r="AB76" s="8" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n"/>
@@ -4029,6 +4600,7 @@
       <c r="Y77" s="8" t="n"/>
       <c r="Z77" s="9" t="n"/>
       <c r="AA77" s="35" t="n"/>
+      <c r="AB77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n"/>
@@ -4058,6 +4630,7 @@
       <c r="Y78" s="8" t="n"/>
       <c r="Z78" s="9" t="n"/>
       <c r="AA78" s="35" t="n"/>
+      <c r="AB78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n"/>
@@ -4087,6 +4660,7 @@
       <c r="Y79" s="8" t="n"/>
       <c r="Z79" s="9" t="n"/>
       <c r="AA79" s="35" t="n"/>
+      <c r="AB79" s="8" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n"/>
@@ -4116,6 +4690,7 @@
       <c r="Y80" s="8" t="n"/>
       <c r="Z80" s="9" t="n"/>
       <c r="AA80" s="35" t="n"/>
+      <c r="AB80" s="8" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n"/>
@@ -4145,6 +4720,7 @@
       <c r="Y81" s="8" t="n"/>
       <c r="Z81" s="9" t="n"/>
       <c r="AA81" s="35" t="n"/>
+      <c r="AB81" s="8" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="8" t="n"/>
@@ -4174,6 +4750,7 @@
       <c r="Y82" s="8" t="n"/>
       <c r="Z82" s="9" t="n"/>
       <c r="AA82" s="35" t="n"/>
+      <c r="AB82" s="8" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n"/>
@@ -4203,6 +4780,7 @@
       <c r="Y83" s="8" t="n"/>
       <c r="Z83" s="9" t="n"/>
       <c r="AA83" s="35" t="n"/>
+      <c r="AB83" s="8" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="8" t="n"/>
@@ -4232,6 +4810,7 @@
       <c r="Y84" s="8" t="n"/>
       <c r="Z84" s="9" t="n"/>
       <c r="AA84" s="35" t="n"/>
+      <c r="AB84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n"/>
@@ -4261,6 +4840,7 @@
       <c r="Y85" s="8" t="n"/>
       <c r="Z85" s="9" t="n"/>
       <c r="AA85" s="35" t="n"/>
+      <c r="AB85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="8" t="n"/>
@@ -4290,6 +4870,7 @@
       <c r="Y86" s="8" t="n"/>
       <c r="Z86" s="9" t="n"/>
       <c r="AA86" s="35" t="n"/>
+      <c r="AB86" s="8" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n"/>
@@ -4319,6 +4900,7 @@
       <c r="Y87" s="8" t="n"/>
       <c r="Z87" s="9" t="n"/>
       <c r="AA87" s="35" t="n"/>
+      <c r="AB87" s="8" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="8" t="n"/>
@@ -4348,6 +4930,7 @@
       <c r="Y88" s="8" t="n"/>
       <c r="Z88" s="9" t="n"/>
       <c r="AA88" s="35" t="n"/>
+      <c r="AB88" s="8" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n"/>
@@ -4377,6 +4960,7 @@
       <c r="Y89" s="8" t="n"/>
       <c r="Z89" s="9" t="n"/>
       <c r="AA89" s="35" t="n"/>
+      <c r="AB89" s="8" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="8" t="n"/>
@@ -4406,6 +4990,7 @@
       <c r="Y90" s="8" t="n"/>
       <c r="Z90" s="9" t="n"/>
       <c r="AA90" s="35" t="n"/>
+      <c r="AB90" s="8" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n"/>
@@ -4435,6 +5020,7 @@
       <c r="Y91" s="8" t="n"/>
       <c r="Z91" s="9" t="n"/>
       <c r="AA91" s="35" t="n"/>
+      <c r="AB91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="8" t="n"/>
@@ -4464,6 +5050,7 @@
       <c r="Y92" s="8" t="n"/>
       <c r="Z92" s="9" t="n"/>
       <c r="AA92" s="35" t="n"/>
+      <c r="AB92" s="8" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n"/>
@@ -4493,6 +5080,7 @@
       <c r="Y93" s="8" t="n"/>
       <c r="Z93" s="9" t="n"/>
       <c r="AA93" s="35" t="n"/>
+      <c r="AB93" s="8" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="8" t="n"/>
@@ -4522,6 +5110,7 @@
       <c r="Y94" s="8" t="n"/>
       <c r="Z94" s="9" t="n"/>
       <c r="AA94" s="35" t="n"/>
+      <c r="AB94" s="8" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n"/>
@@ -4551,6 +5140,7 @@
       <c r="Y95" s="8" t="n"/>
       <c r="Z95" s="9" t="n"/>
       <c r="AA95" s="35" t="n"/>
+      <c r="AB95" s="8" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="n"/>
@@ -4580,6 +5170,7 @@
       <c r="Y96" s="8" t="n"/>
       <c r="Z96" s="9" t="n"/>
       <c r="AA96" s="35" t="n"/>
+      <c r="AB96" s="8" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n"/>
@@ -4609,6 +5200,7 @@
       <c r="Y97" s="8" t="n"/>
       <c r="Z97" s="9" t="n"/>
       <c r="AA97" s="35" t="n"/>
+      <c r="AB97" s="8" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="8" t="n"/>
@@ -4638,6 +5230,7 @@
       <c r="Y98" s="8" t="n"/>
       <c r="Z98" s="9" t="n"/>
       <c r="AA98" s="35" t="n"/>
+      <c r="AB98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n"/>
@@ -4667,6 +5260,7 @@
       <c r="Y99" s="8" t="n"/>
       <c r="Z99" s="9" t="n"/>
       <c r="AA99" s="35" t="n"/>
+      <c r="AB99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="8" t="n"/>
@@ -4696,6 +5290,7 @@
       <c r="Y100" s="8" t="n"/>
       <c r="Z100" s="9" t="n"/>
       <c r="AA100" s="35" t="n"/>
+      <c r="AB100" s="8" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n"/>
@@ -4725,6 +5320,7 @@
       <c r="Y101" s="8" t="n"/>
       <c r="Z101" s="9" t="n"/>
       <c r="AA101" s="35" t="n"/>
+      <c r="AB101" s="8" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="8" t="n"/>
@@ -4754,6 +5350,7 @@
       <c r="Y102" s="8" t="n"/>
       <c r="Z102" s="9" t="n"/>
       <c r="AA102" s="35" t="n"/>
+      <c r="AB102" s="8" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="n"/>
@@ -4783,6 +5380,7 @@
       <c r="Y103" s="8" t="n"/>
       <c r="Z103" s="9" t="n"/>
       <c r="AA103" s="35" t="n"/>
+      <c r="AB103" s="8" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="8" t="n"/>
@@ -4812,6 +5410,7 @@
       <c r="Y104" s="8" t="n"/>
       <c r="Z104" s="9" t="n"/>
       <c r="AA104" s="35" t="n"/>
+      <c r="AB104" s="8" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="n"/>
@@ -4841,6 +5440,7 @@
       <c r="Y105" s="8" t="n"/>
       <c r="Z105" s="9" t="n"/>
       <c r="AA105" s="35" t="n"/>
+      <c r="AB105" s="8" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="8" t="n"/>
@@ -4870,6 +5470,7 @@
       <c r="Y106" s="8" t="n"/>
       <c r="Z106" s="9" t="n"/>
       <c r="AA106" s="35" t="n"/>
+      <c r="AB106" s="8" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="n"/>
@@ -4899,6 +5500,7 @@
       <c r="Y107" s="8" t="n"/>
       <c r="Z107" s="9" t="n"/>
       <c r="AA107" s="35" t="n"/>
+      <c r="AB107" s="8" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="8" t="n"/>
@@ -4928,6 +5530,7 @@
       <c r="Y108" s="8" t="n"/>
       <c r="Z108" s="9" t="n"/>
       <c r="AA108" s="35" t="n"/>
+      <c r="AB108" s="8" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="n"/>
@@ -4957,6 +5560,7 @@
       <c r="Y109" s="8" t="n"/>
       <c r="Z109" s="9" t="n"/>
       <c r="AA109" s="35" t="n"/>
+      <c r="AB109" s="8" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="8" t="n"/>
@@ -4986,6 +5590,7 @@
       <c r="Y110" s="8" t="n"/>
       <c r="Z110" s="9" t="n"/>
       <c r="AA110" s="35" t="n"/>
+      <c r="AB110" s="8" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="n"/>
@@ -5015,6 +5620,7 @@
       <c r="Y111" s="8" t="n"/>
       <c r="Z111" s="9" t="n"/>
       <c r="AA111" s="35" t="n"/>
+      <c r="AB111" s="8" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="8" t="n"/>
@@ -5044,6 +5650,7 @@
       <c r="Y112" s="8" t="n"/>
       <c r="Z112" s="9" t="n"/>
       <c r="AA112" s="35" t="n"/>
+      <c r="AB112" s="8" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="n"/>
@@ -5073,6 +5680,7 @@
       <c r="Y113" s="8" t="n"/>
       <c r="Z113" s="9" t="n"/>
       <c r="AA113" s="35" t="n"/>
+      <c r="AB113" s="8" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="8" t="n"/>
@@ -5102,6 +5710,7 @@
       <c r="Y114" s="8" t="n"/>
       <c r="Z114" s="9" t="n"/>
       <c r="AA114" s="35" t="n"/>
+      <c r="AB114" s="8" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="n"/>
@@ -5131,6 +5740,7 @@
       <c r="Y115" s="8" t="n"/>
       <c r="Z115" s="9" t="n"/>
       <c r="AA115" s="35" t="n"/>
+      <c r="AB115" s="8" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="8" t="n"/>
@@ -5160,6 +5770,7 @@
       <c r="Y116" s="8" t="n"/>
       <c r="Z116" s="9" t="n"/>
       <c r="AA116" s="35" t="n"/>
+      <c r="AB116" s="8" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="n"/>
@@ -5189,6 +5800,7 @@
       <c r="Y117" s="8" t="n"/>
       <c r="Z117" s="9" t="n"/>
       <c r="AA117" s="35" t="n"/>
+      <c r="AB117" s="8" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="8" t="n"/>
@@ -5218,6 +5830,7 @@
       <c r="Y118" s="8" t="n"/>
       <c r="Z118" s="9" t="n"/>
       <c r="AA118" s="35" t="n"/>
+      <c r="AB118" s="8" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="n"/>
@@ -5247,6 +5860,7 @@
       <c r="Y119" s="8" t="n"/>
       <c r="Z119" s="9" t="n"/>
       <c r="AA119" s="35" t="n"/>
+      <c r="AB119" s="8" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="8" t="n"/>
@@ -5276,6 +5890,7 @@
       <c r="Y120" s="8" t="n"/>
       <c r="Z120" s="9" t="n"/>
       <c r="AA120" s="35" t="n"/>
+      <c r="AB120" s="8" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="AB3:AB120">

--- a/willitboard_operadores.xlsx
+++ b/willitboard_operadores.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1131,6 +1131,18 @@
       <c r="B53" s="21" t="inlineStr">
         <is>
           <t>Columna AB, opcional, solo para aerolíneas con límite dimensional. Nombre de la tarifa a la que corresponden las cifras, copiado tal como lo escribe el operador en su página oficial (por ejemplo "Basic"). No se traduce. Vacía significa "no confirmada": la ficha muestra entonces el aviso genérico de tarifas. Se completa solo después de que Marcos confirma el nombre en la fuente, igual que cualquier otro dato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="21" t="inlineStr">
+        <is>
+          <t>peso_combinado_kg (esquema 1.4, 26/09/2026)</t>
+        </is>
+      </c>
+      <c r="B54" s="21" t="inlineStr">
+        <is>
+          <t>Columna AC, opcional. Solo cuando el operador publica UN peso para el artículo personal y la valija juntos (por ejemplo "12 kg en total"). No se reparte entre los bultos. Si además publica un peso por bulto, va en personal_kg o cabina_kg, y el conversor rechaza un peso por bulto mayor que el combinado. En la ficha se lee "X kg en total entre los dos bultos"; en el comparador, una valija sola que pesa más que el total no entra.</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB120"/>
+  <dimension ref="A1:AC120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1176,6 +1188,7 @@
     <col width="46" customWidth="1" min="26" max="26"/>
     <col width="21" customWidth="1" min="27" max="27"/>
     <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1319,6 +1332,11 @@
           <t>tarifa_referencia</t>
         </is>
       </c>
+      <c r="AC1" s="17" t="inlineStr">
+        <is>
+          <t>peso_combinado_kg</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
@@ -1459,6 +1477,11 @@
       <c r="AB2" s="6" t="inlineStr">
         <is>
           <t>nombre de la tarifa tal como lo escribe el operador; solo aerolíneas</t>
+        </is>
+      </c>
+      <c r="AC2" s="6" t="inlineStr">
+        <is>
+          <t>kg para artículo personal + valija JUNTOS, solo si el operador lo publica así</t>
         </is>
       </c>
     </row>
@@ -1551,6 +1574,7 @@
         <v>46277</v>
       </c>
       <c r="AB3" s="15" t="n"/>
+      <c r="AC3" s="13" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -1649,6 +1673,7 @@
         <v>46277</v>
       </c>
       <c r="AB4" s="8" t="n"/>
+      <c r="AC4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -1747,6 +1772,7 @@
         </is>
       </c>
       <c r="AB5" s="8" t="n"/>
+      <c r="AC5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="33" t="inlineStr">
@@ -1817,6 +1843,7 @@
         </is>
       </c>
       <c r="AB6" s="33" t="n"/>
+      <c r="AC6" s="33" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="33" t="inlineStr">
@@ -1887,6 +1914,7 @@
         </is>
       </c>
       <c r="AB7" s="33" t="n"/>
+      <c r="AC7" s="33" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="33" t="inlineStr">
@@ -1957,6 +1985,7 @@
         </is>
       </c>
       <c r="AB8" s="33" t="n"/>
+      <c r="AC8" s="33" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -2047,6 +2076,7 @@
         </is>
       </c>
       <c r="AB9" s="8" t="n"/>
+      <c r="AC9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="33" t="inlineStr">
@@ -2117,6 +2147,7 @@
         </is>
       </c>
       <c r="AB10" s="33" t="n"/>
+      <c r="AC10" s="33" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -2205,6 +2236,7 @@
           <t>Fly Light</t>
         </is>
       </c>
+      <c r="AC11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -2297,6 +2329,7 @@
           <t>Economy Basic</t>
         </is>
       </c>
+      <c r="AC12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -2385,6 +2418,7 @@
           <t>Economy Light</t>
         </is>
       </c>
+      <c r="AC13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -2463,7 +2497,7 @@
       <c r="X14" s="8" t="n"/>
       <c r="Y14" s="8" t="inlineStr">
         <is>
-          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. BLOQUEADA POR ESQUEMA: LowFare incluye solo el bolso bajo el asiento (30x40x20 cm, máx. 10 kg). LowFare+ suma la valija 55x40x23 cm con PESO COMBINADO de 10 kg para los dos bultos; Flex, 15 kg combinados. El esquema guarda peso por bulto: dejar cabina_kg vacío haría que la ficha diga "sin límite de peso publicado", que es falso. No publicar hasta decidir cómo se modela el peso combinado. [NO SÉ] ruedas/asas.</t>
+          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. PESO COMBINADO (columna peso_combinado_kg, 26/09/2026): LowFare incluye solo el bolso bajo el asiento (30x40x20 cm, máx. 10 kg). LowFare+ suma la valija 55x40x23 cm con PESO COMBINADO de 10 kg para los dos bultos; Flex, 15 kg combinados. El esquema guarda peso por bulto: dejar cabina_kg vacío haría que la ficha diga "sin límite de peso publicado", que es falso. [NO SÉ] ruedas/asas. Se carga peso_combinado_kg = 10 (LowFare+) y personal_kg = 10 (LowFare). Flex, 15 kg combinados: no se modela porque la fila describe LowFare.</t>
         </is>
       </c>
       <c r="Z14" s="9" t="inlineStr">
@@ -2476,6 +2510,9 @@
         <is>
           <t>LowFare</t>
         </is>
+      </c>
+      <c r="AC14" s="8" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -2557,7 +2594,7 @@
       <c r="X15" s="8" t="n"/>
       <c r="Y15" s="8" t="inlineStr">
         <is>
-          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. BLOQUEADA POR ESQUEMA: en Economy el peso es COMBINADO, 12 kg entre la valija y el bolso pequeño. Bolso pequeño 40x30x15 cm; valija 55x35x25 cm "including pockets, wheels, and handles". Las tarifas Basic incluyen solo el bolso pequeño; la valija requiere Flying Blue Gold+ o comprar la opción. Confirmar el nombre exacto de la tarifa (Basic o Light) y del extra.</t>
+          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. PESO COMBINADO (columna peso_combinado_kg, 26/09/2026): en Economy el peso es COMBINADO, 12 kg entre la valija y el bolso pequeño. Bolso pequeño 40x30x15 cm; valija 55x35x25 cm "including pockets, wheels, and handles". Las tarifas Basic incluyen solo el bolso pequeño; la valija requiere Flying Blue Gold+ o comprar la opción. Confirmar el nombre exacto de la tarifa (Basic o Light) y del extra. Se carga peso_combinado_kg = 12; los pesos por bulto quedan vacíos porque Air France no los publica por separado.</t>
         </is>
       </c>
       <c r="Z15" s="9" t="inlineStr">
@@ -2570,6 +2607,9 @@
         <is>
           <t>Basic</t>
         </is>
+      </c>
+      <c r="AC15" s="8" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -2647,7 +2687,7 @@
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="8" t="inlineStr">
         <is>
-          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. BLOQUEADA POR ESQUEMA: peso COMBINADO de 12 kg entre bolso pequeño y valija en Economy. Bolso pequeño 40x30x15 cm bajo el asiento; valija 55x35x25 cm "including handles and wheels". Economy Light, Standard y Flex incluyen la valija; Basic solo el bolso pequeño. [NO SÉ] nombre del extra.</t>
+          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. PESO COMBINADO (columna peso_combinado_kg, 26/09/2026): peso COMBINADO de 12 kg entre bolso pequeño y valija en Economy. Bolso pequeño 40x30x15 cm bajo el asiento; valija 55x35x25 cm "including handles and wheels". Economy Light, Standard y Flex incluyen la valija; Basic solo el bolso pequeño. [NO SÉ] nombre del extra. Se carga peso_combinado_kg = 12; pesos por bulto vacíos.</t>
         </is>
       </c>
       <c r="Z16" s="9" t="inlineStr">
@@ -2661,6 +2701,9 @@
           <t>Economy Basic</t>
         </is>
       </c>
+      <c r="AC16" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -2707,7 +2750,9 @@
       <c r="J17" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="K17" s="8" t="n"/>
+      <c r="K17" s="8" t="n">
+        <v>10</v>
+      </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2741,7 +2786,7 @@
       <c r="X17" s="8" t="n"/>
       <c r="Y17" s="8" t="inlineStr">
         <is>
-          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. BLOQUEADA POR ESQUEMA: bolso pequeño 40x30x20 cm y hasta 10 kg; con valija 55x40x25 cm el PESO ES COMBINADO, 10 kg entre los dos. Medidas "including wheels and handles". Basic y Plus no incluyen la valija; Smart y Max sí, con Priority Boarding. cabina_addon es descripción del asistente: confirmar el nombre comercial.</t>
+          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. PESO COMBINADO (columna peso_combinado_kg, 26/09/2026): bolso pequeño 40x30x20 cm y hasta 10 kg; con valija 55x40x25 cm el PESO ES COMBINADO, 10 kg entre los dos. Medidas "including wheels and handles". Basic y Plus no incluyen la valija; Smart y Max sí, con Priority Boarding. cabina_addon es descripción del asistente: confirmar el nombre comercial. Se carga personal_kg = 10 y peso_combinado_kg = 10.</t>
         </is>
       </c>
       <c r="Z17" s="9" t="inlineStr">
@@ -2754,6 +2799,9 @@
         <is>
           <t>Basic</t>
         </is>
+      </c>
+      <c r="AC17" s="8" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -2831,6 +2879,7 @@
       </c>
       <c r="AA18" s="35" t="n"/>
       <c r="AB18" s="8" t="n"/>
+      <c r="AC18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n"/>
@@ -2861,6 +2910,7 @@
       <c r="Z19" s="9" t="n"/>
       <c r="AA19" s="35" t="n"/>
       <c r="AB19" s="8" t="n"/>
+      <c r="AC19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n"/>
@@ -2891,6 +2941,7 @@
       <c r="Z20" s="9" t="n"/>
       <c r="AA20" s="35" t="n"/>
       <c r="AB20" s="8" t="n"/>
+      <c r="AC20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n"/>
@@ -2921,6 +2972,7 @@
       <c r="Z21" s="9" t="n"/>
       <c r="AA21" s="35" t="n"/>
       <c r="AB21" s="8" t="n"/>
+      <c r="AC21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n"/>
@@ -2951,6 +3003,7 @@
       <c r="Z22" s="9" t="n"/>
       <c r="AA22" s="35" t="n"/>
       <c r="AB22" s="8" t="n"/>
+      <c r="AC22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n"/>
@@ -2981,6 +3034,7 @@
       <c r="Z23" s="9" t="n"/>
       <c r="AA23" s="35" t="n"/>
       <c r="AB23" s="8" t="n"/>
+      <c r="AC23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n"/>
@@ -3011,6 +3065,7 @@
       <c r="Z24" s="9" t="n"/>
       <c r="AA24" s="35" t="n"/>
       <c r="AB24" s="8" t="n"/>
+      <c r="AC24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n"/>
@@ -3041,6 +3096,7 @@
       <c r="Z25" s="9" t="n"/>
       <c r="AA25" s="35" t="n"/>
       <c r="AB25" s="8" t="n"/>
+      <c r="AC25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n"/>
@@ -3071,6 +3127,7 @@
       <c r="Z26" s="9" t="n"/>
       <c r="AA26" s="35" t="n"/>
       <c r="AB26" s="8" t="n"/>
+      <c r="AC26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n"/>
@@ -3101,6 +3158,7 @@
       <c r="Z27" s="9" t="n"/>
       <c r="AA27" s="35" t="n"/>
       <c r="AB27" s="8" t="n"/>
+      <c r="AC27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n"/>
@@ -3131,6 +3189,7 @@
       <c r="Z28" s="9" t="n"/>
       <c r="AA28" s="35" t="n"/>
       <c r="AB28" s="8" t="n"/>
+      <c r="AC28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n"/>
@@ -3161,6 +3220,7 @@
       <c r="Z29" s="9" t="n"/>
       <c r="AA29" s="35" t="n"/>
       <c r="AB29" s="8" t="n"/>
+      <c r="AC29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n"/>
@@ -3191,6 +3251,7 @@
       <c r="Z30" s="9" t="n"/>
       <c r="AA30" s="35" t="n"/>
       <c r="AB30" s="8" t="n"/>
+      <c r="AC30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
@@ -3221,6 +3282,7 @@
       <c r="Z31" s="9" t="n"/>
       <c r="AA31" s="35" t="n"/>
       <c r="AB31" s="8" t="n"/>
+      <c r="AC31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n"/>
@@ -3251,6 +3313,7 @@
       <c r="Z32" s="9" t="n"/>
       <c r="AA32" s="35" t="n"/>
       <c r="AB32" s="8" t="n"/>
+      <c r="AC32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
@@ -3281,6 +3344,7 @@
       <c r="Z33" s="9" t="n"/>
       <c r="AA33" s="35" t="n"/>
       <c r="AB33" s="8" t="n"/>
+      <c r="AC33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n"/>
@@ -3311,6 +3375,7 @@
       <c r="Z34" s="9" t="n"/>
       <c r="AA34" s="35" t="n"/>
       <c r="AB34" s="8" t="n"/>
+      <c r="AC34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
@@ -3341,6 +3406,7 @@
       <c r="Z35" s="9" t="n"/>
       <c r="AA35" s="35" t="n"/>
       <c r="AB35" s="8" t="n"/>
+      <c r="AC35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n"/>
@@ -3371,6 +3437,7 @@
       <c r="Z36" s="9" t="n"/>
       <c r="AA36" s="35" t="n"/>
       <c r="AB36" s="8" t="n"/>
+      <c r="AC36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
@@ -3401,6 +3468,7 @@
       <c r="Z37" s="9" t="n"/>
       <c r="AA37" s="35" t="n"/>
       <c r="AB37" s="8" t="n"/>
+      <c r="AC37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n"/>
@@ -3431,6 +3499,7 @@
       <c r="Z38" s="9" t="n"/>
       <c r="AA38" s="35" t="n"/>
       <c r="AB38" s="8" t="n"/>
+      <c r="AC38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
@@ -3461,6 +3530,7 @@
       <c r="Z39" s="9" t="n"/>
       <c r="AA39" s="35" t="n"/>
       <c r="AB39" s="8" t="n"/>
+      <c r="AC39" s="8" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n"/>
@@ -3491,6 +3561,7 @@
       <c r="Z40" s="9" t="n"/>
       <c r="AA40" s="35" t="n"/>
       <c r="AB40" s="8" t="n"/>
+      <c r="AC40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
@@ -3521,6 +3592,7 @@
       <c r="Z41" s="9" t="n"/>
       <c r="AA41" s="35" t="n"/>
       <c r="AB41" s="8" t="n"/>
+      <c r="AC41" s="8" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n"/>
@@ -3551,6 +3623,7 @@
       <c r="Z42" s="9" t="n"/>
       <c r="AA42" s="35" t="n"/>
       <c r="AB42" s="8" t="n"/>
+      <c r="AC42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n"/>
@@ -3581,6 +3654,7 @@
       <c r="Z43" s="9" t="n"/>
       <c r="AA43" s="35" t="n"/>
       <c r="AB43" s="8" t="n"/>
+      <c r="AC43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n"/>
@@ -3611,6 +3685,7 @@
       <c r="Z44" s="9" t="n"/>
       <c r="AA44" s="35" t="n"/>
       <c r="AB44" s="8" t="n"/>
+      <c r="AC44" s="8" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n"/>
@@ -3641,6 +3716,7 @@
       <c r="Z45" s="9" t="n"/>
       <c r="AA45" s="35" t="n"/>
       <c r="AB45" s="8" t="n"/>
+      <c r="AC45" s="8" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n"/>
@@ -3671,6 +3747,7 @@
       <c r="Z46" s="9" t="n"/>
       <c r="AA46" s="35" t="n"/>
       <c r="AB46" s="8" t="n"/>
+      <c r="AC46" s="8" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n"/>
@@ -3701,6 +3778,7 @@
       <c r="Z47" s="9" t="n"/>
       <c r="AA47" s="35" t="n"/>
       <c r="AB47" s="8" t="n"/>
+      <c r="AC47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n"/>
@@ -3731,6 +3809,7 @@
       <c r="Z48" s="9" t="n"/>
       <c r="AA48" s="35" t="n"/>
       <c r="AB48" s="8" t="n"/>
+      <c r="AC48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
@@ -3761,6 +3840,7 @@
       <c r="Z49" s="9" t="n"/>
       <c r="AA49" s="35" t="n"/>
       <c r="AB49" s="8" t="n"/>
+      <c r="AC49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n"/>
@@ -3791,6 +3871,7 @@
       <c r="Z50" s="9" t="n"/>
       <c r="AA50" s="35" t="n"/>
       <c r="AB50" s="8" t="n"/>
+      <c r="AC50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n"/>
@@ -3821,6 +3902,7 @@
       <c r="Z51" s="9" t="n"/>
       <c r="AA51" s="35" t="n"/>
       <c r="AB51" s="8" t="n"/>
+      <c r="AC51" s="8" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n"/>
@@ -3851,6 +3933,7 @@
       <c r="Z52" s="9" t="n"/>
       <c r="AA52" s="35" t="n"/>
       <c r="AB52" s="8" t="n"/>
+      <c r="AC52" s="8" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
@@ -3881,6 +3964,7 @@
       <c r="Z53" s="9" t="n"/>
       <c r="AA53" s="35" t="n"/>
       <c r="AB53" s="8" t="n"/>
+      <c r="AC53" s="8" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n"/>
@@ -3911,6 +3995,7 @@
       <c r="Z54" s="9" t="n"/>
       <c r="AA54" s="35" t="n"/>
       <c r="AB54" s="8" t="n"/>
+      <c r="AC54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
@@ -3941,6 +4026,7 @@
       <c r="Z55" s="9" t="n"/>
       <c r="AA55" s="35" t="n"/>
       <c r="AB55" s="8" t="n"/>
+      <c r="AC55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n"/>
@@ -3971,6 +4057,7 @@
       <c r="Z56" s="9" t="n"/>
       <c r="AA56" s="35" t="n"/>
       <c r="AB56" s="8" t="n"/>
+      <c r="AC56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
@@ -4001,6 +4088,7 @@
       <c r="Z57" s="9" t="n"/>
       <c r="AA57" s="35" t="n"/>
       <c r="AB57" s="8" t="n"/>
+      <c r="AC57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n"/>
@@ -4031,6 +4119,7 @@
       <c r="Z58" s="9" t="n"/>
       <c r="AA58" s="35" t="n"/>
       <c r="AB58" s="8" t="n"/>
+      <c r="AC58" s="8" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
@@ -4061,6 +4150,7 @@
       <c r="Z59" s="9" t="n"/>
       <c r="AA59" s="35" t="n"/>
       <c r="AB59" s="8" t="n"/>
+      <c r="AC59" s="8" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n"/>
@@ -4091,6 +4181,7 @@
       <c r="Z60" s="9" t="n"/>
       <c r="AA60" s="35" t="n"/>
       <c r="AB60" s="8" t="n"/>
+      <c r="AC60" s="8" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
@@ -4121,6 +4212,7 @@
       <c r="Z61" s="9" t="n"/>
       <c r="AA61" s="35" t="n"/>
       <c r="AB61" s="8" t="n"/>
+      <c r="AC61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n"/>
@@ -4151,6 +4243,7 @@
       <c r="Z62" s="9" t="n"/>
       <c r="AA62" s="35" t="n"/>
       <c r="AB62" s="8" t="n"/>
+      <c r="AC62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n"/>
@@ -4181,6 +4274,7 @@
       <c r="Z63" s="9" t="n"/>
       <c r="AA63" s="35" t="n"/>
       <c r="AB63" s="8" t="n"/>
+      <c r="AC63" s="8" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n"/>
@@ -4211,6 +4305,7 @@
       <c r="Z64" s="9" t="n"/>
       <c r="AA64" s="35" t="n"/>
       <c r="AB64" s="8" t="n"/>
+      <c r="AC64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n"/>
@@ -4241,6 +4336,7 @@
       <c r="Z65" s="9" t="n"/>
       <c r="AA65" s="35" t="n"/>
       <c r="AB65" s="8" t="n"/>
+      <c r="AC65" s="8" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n"/>
@@ -4271,6 +4367,7 @@
       <c r="Z66" s="9" t="n"/>
       <c r="AA66" s="35" t="n"/>
       <c r="AB66" s="8" t="n"/>
+      <c r="AC66" s="8" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n"/>
@@ -4301,6 +4398,7 @@
       <c r="Z67" s="9" t="n"/>
       <c r="AA67" s="35" t="n"/>
       <c r="AB67" s="8" t="n"/>
+      <c r="AC67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n"/>
@@ -4331,6 +4429,7 @@
       <c r="Z68" s="9" t="n"/>
       <c r="AA68" s="35" t="n"/>
       <c r="AB68" s="8" t="n"/>
+      <c r="AC68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
@@ -4361,6 +4460,7 @@
       <c r="Z69" s="9" t="n"/>
       <c r="AA69" s="35" t="n"/>
       <c r="AB69" s="8" t="n"/>
+      <c r="AC69" s="8" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n"/>
@@ -4391,6 +4491,7 @@
       <c r="Z70" s="9" t="n"/>
       <c r="AA70" s="35" t="n"/>
       <c r="AB70" s="8" t="n"/>
+      <c r="AC70" s="8" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
@@ -4421,6 +4522,7 @@
       <c r="Z71" s="9" t="n"/>
       <c r="AA71" s="35" t="n"/>
       <c r="AB71" s="8" t="n"/>
+      <c r="AC71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n"/>
@@ -4451,6 +4553,7 @@
       <c r="Z72" s="9" t="n"/>
       <c r="AA72" s="35" t="n"/>
       <c r="AB72" s="8" t="n"/>
+      <c r="AC72" s="8" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
@@ -4481,6 +4584,7 @@
       <c r="Z73" s="9" t="n"/>
       <c r="AA73" s="35" t="n"/>
       <c r="AB73" s="8" t="n"/>
+      <c r="AC73" s="8" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n"/>
@@ -4511,6 +4615,7 @@
       <c r="Z74" s="9" t="n"/>
       <c r="AA74" s="35" t="n"/>
       <c r="AB74" s="8" t="n"/>
+      <c r="AC74" s="8" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n"/>
@@ -4541,6 +4646,7 @@
       <c r="Z75" s="9" t="n"/>
       <c r="AA75" s="35" t="n"/>
       <c r="AB75" s="8" t="n"/>
+      <c r="AC75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="n"/>
@@ -4571,6 +4677,7 @@
       <c r="Z76" s="9" t="n"/>
       <c r="AA76" s="35" t="n"/>
       <c r="AB76" s="8" t="n"/>
+      <c r="AC76" s="8" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n"/>
@@ -4601,6 +4708,7 @@
       <c r="Z77" s="9" t="n"/>
       <c r="AA77" s="35" t="n"/>
       <c r="AB77" s="8" t="n"/>
+      <c r="AC77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n"/>
@@ -4631,6 +4739,7 @@
       <c r="Z78" s="9" t="n"/>
       <c r="AA78" s="35" t="n"/>
       <c r="AB78" s="8" t="n"/>
+      <c r="AC78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n"/>
@@ -4661,6 +4770,7 @@
       <c r="Z79" s="9" t="n"/>
       <c r="AA79" s="35" t="n"/>
       <c r="AB79" s="8" t="n"/>
+      <c r="AC79" s="8" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n"/>
@@ -4691,6 +4801,7 @@
       <c r="Z80" s="9" t="n"/>
       <c r="AA80" s="35" t="n"/>
       <c r="AB80" s="8" t="n"/>
+      <c r="AC80" s="8" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n"/>
@@ -4721,6 +4832,7 @@
       <c r="Z81" s="9" t="n"/>
       <c r="AA81" s="35" t="n"/>
       <c r="AB81" s="8" t="n"/>
+      <c r="AC81" s="8" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="8" t="n"/>
@@ -4751,6 +4863,7 @@
       <c r="Z82" s="9" t="n"/>
       <c r="AA82" s="35" t="n"/>
       <c r="AB82" s="8" t="n"/>
+      <c r="AC82" s="8" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n"/>
@@ -4781,6 +4894,7 @@
       <c r="Z83" s="9" t="n"/>
       <c r="AA83" s="35" t="n"/>
       <c r="AB83" s="8" t="n"/>
+      <c r="AC83" s="8" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="8" t="n"/>
@@ -4811,6 +4925,7 @@
       <c r="Z84" s="9" t="n"/>
       <c r="AA84" s="35" t="n"/>
       <c r="AB84" s="8" t="n"/>
+      <c r="AC84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n"/>
@@ -4841,6 +4956,7 @@
       <c r="Z85" s="9" t="n"/>
       <c r="AA85" s="35" t="n"/>
       <c r="AB85" s="8" t="n"/>
+      <c r="AC85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="8" t="n"/>
@@ -4871,6 +4987,7 @@
       <c r="Z86" s="9" t="n"/>
       <c r="AA86" s="35" t="n"/>
       <c r="AB86" s="8" t="n"/>
+      <c r="AC86" s="8" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n"/>
@@ -4901,6 +5018,7 @@
       <c r="Z87" s="9" t="n"/>
       <c r="AA87" s="35" t="n"/>
       <c r="AB87" s="8" t="n"/>
+      <c r="AC87" s="8" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="8" t="n"/>
@@ -4931,6 +5049,7 @@
       <c r="Z88" s="9" t="n"/>
       <c r="AA88" s="35" t="n"/>
       <c r="AB88" s="8" t="n"/>
+      <c r="AC88" s="8" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n"/>
@@ -4961,6 +5080,7 @@
       <c r="Z89" s="9" t="n"/>
       <c r="AA89" s="35" t="n"/>
       <c r="AB89" s="8" t="n"/>
+      <c r="AC89" s="8" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="8" t="n"/>
@@ -4991,6 +5111,7 @@
       <c r="Z90" s="9" t="n"/>
       <c r="AA90" s="35" t="n"/>
       <c r="AB90" s="8" t="n"/>
+      <c r="AC90" s="8" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n"/>
@@ -5021,6 +5142,7 @@
       <c r="Z91" s="9" t="n"/>
       <c r="AA91" s="35" t="n"/>
       <c r="AB91" s="8" t="n"/>
+      <c r="AC91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="8" t="n"/>
@@ -5051,6 +5173,7 @@
       <c r="Z92" s="9" t="n"/>
       <c r="AA92" s="35" t="n"/>
       <c r="AB92" s="8" t="n"/>
+      <c r="AC92" s="8" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n"/>
@@ -5081,6 +5204,7 @@
       <c r="Z93" s="9" t="n"/>
       <c r="AA93" s="35" t="n"/>
       <c r="AB93" s="8" t="n"/>
+      <c r="AC93" s="8" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="8" t="n"/>
@@ -5111,6 +5235,7 @@
       <c r="Z94" s="9" t="n"/>
       <c r="AA94" s="35" t="n"/>
       <c r="AB94" s="8" t="n"/>
+      <c r="AC94" s="8" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n"/>
@@ -5141,6 +5266,7 @@
       <c r="Z95" s="9" t="n"/>
       <c r="AA95" s="35" t="n"/>
       <c r="AB95" s="8" t="n"/>
+      <c r="AC95" s="8" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="n"/>
@@ -5171,6 +5297,7 @@
       <c r="Z96" s="9" t="n"/>
       <c r="AA96" s="35" t="n"/>
       <c r="AB96" s="8" t="n"/>
+      <c r="AC96" s="8" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n"/>
@@ -5201,6 +5328,7 @@
       <c r="Z97" s="9" t="n"/>
       <c r="AA97" s="35" t="n"/>
       <c r="AB97" s="8" t="n"/>
+      <c r="AC97" s="8" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="8" t="n"/>
@@ -5231,6 +5359,7 @@
       <c r="Z98" s="9" t="n"/>
       <c r="AA98" s="35" t="n"/>
       <c r="AB98" s="8" t="n"/>
+      <c r="AC98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n"/>
@@ -5261,6 +5390,7 @@
       <c r="Z99" s="9" t="n"/>
       <c r="AA99" s="35" t="n"/>
       <c r="AB99" s="8" t="n"/>
+      <c r="AC99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="8" t="n"/>
@@ -5291,6 +5421,7 @@
       <c r="Z100" s="9" t="n"/>
       <c r="AA100" s="35" t="n"/>
       <c r="AB100" s="8" t="n"/>
+      <c r="AC100" s="8" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n"/>
@@ -5321,6 +5452,7 @@
       <c r="Z101" s="9" t="n"/>
       <c r="AA101" s="35" t="n"/>
       <c r="AB101" s="8" t="n"/>
+      <c r="AC101" s="8" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="8" t="n"/>
@@ -5351,6 +5483,7 @@
       <c r="Z102" s="9" t="n"/>
       <c r="AA102" s="35" t="n"/>
       <c r="AB102" s="8" t="n"/>
+      <c r="AC102" s="8" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="n"/>
@@ -5381,6 +5514,7 @@
       <c r="Z103" s="9" t="n"/>
       <c r="AA103" s="35" t="n"/>
       <c r="AB103" s="8" t="n"/>
+      <c r="AC103" s="8" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="8" t="n"/>
@@ -5411,6 +5545,7 @@
       <c r="Z104" s="9" t="n"/>
       <c r="AA104" s="35" t="n"/>
       <c r="AB104" s="8" t="n"/>
+      <c r="AC104" s="8" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="n"/>
@@ -5441,6 +5576,7 @@
       <c r="Z105" s="9" t="n"/>
       <c r="AA105" s="35" t="n"/>
       <c r="AB105" s="8" t="n"/>
+      <c r="AC105" s="8" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="8" t="n"/>
@@ -5471,6 +5607,7 @@
       <c r="Z106" s="9" t="n"/>
       <c r="AA106" s="35" t="n"/>
       <c r="AB106" s="8" t="n"/>
+      <c r="AC106" s="8" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="n"/>
@@ -5501,6 +5638,7 @@
       <c r="Z107" s="9" t="n"/>
       <c r="AA107" s="35" t="n"/>
       <c r="AB107" s="8" t="n"/>
+      <c r="AC107" s="8" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="8" t="n"/>
@@ -5531,6 +5669,7 @@
       <c r="Z108" s="9" t="n"/>
       <c r="AA108" s="35" t="n"/>
       <c r="AB108" s="8" t="n"/>
+      <c r="AC108" s="8" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="n"/>
@@ -5561,6 +5700,7 @@
       <c r="Z109" s="9" t="n"/>
       <c r="AA109" s="35" t="n"/>
       <c r="AB109" s="8" t="n"/>
+      <c r="AC109" s="8" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="8" t="n"/>
@@ -5591,6 +5731,7 @@
       <c r="Z110" s="9" t="n"/>
       <c r="AA110" s="35" t="n"/>
       <c r="AB110" s="8" t="n"/>
+      <c r="AC110" s="8" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="n"/>
@@ -5621,6 +5762,7 @@
       <c r="Z111" s="9" t="n"/>
       <c r="AA111" s="35" t="n"/>
       <c r="AB111" s="8" t="n"/>
+      <c r="AC111" s="8" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="8" t="n"/>
@@ -5651,6 +5793,7 @@
       <c r="Z112" s="9" t="n"/>
       <c r="AA112" s="35" t="n"/>
       <c r="AB112" s="8" t="n"/>
+      <c r="AC112" s="8" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="n"/>
@@ -5681,6 +5824,7 @@
       <c r="Z113" s="9" t="n"/>
       <c r="AA113" s="35" t="n"/>
       <c r="AB113" s="8" t="n"/>
+      <c r="AC113" s="8" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="8" t="n"/>
@@ -5711,6 +5855,7 @@
       <c r="Z114" s="9" t="n"/>
       <c r="AA114" s="35" t="n"/>
       <c r="AB114" s="8" t="n"/>
+      <c r="AC114" s="8" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="n"/>
@@ -5741,6 +5886,7 @@
       <c r="Z115" s="9" t="n"/>
       <c r="AA115" s="35" t="n"/>
       <c r="AB115" s="8" t="n"/>
+      <c r="AC115" s="8" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="8" t="n"/>
@@ -5771,6 +5917,7 @@
       <c r="Z116" s="9" t="n"/>
       <c r="AA116" s="35" t="n"/>
       <c r="AB116" s="8" t="n"/>
+      <c r="AC116" s="8" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="n"/>
@@ -5801,6 +5948,7 @@
       <c r="Z117" s="9" t="n"/>
       <c r="AA117" s="35" t="n"/>
       <c r="AB117" s="8" t="n"/>
+      <c r="AC117" s="8" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="8" t="n"/>
@@ -5831,6 +5979,7 @@
       <c r="Z118" s="9" t="n"/>
       <c r="AA118" s="35" t="n"/>
       <c r="AB118" s="8" t="n"/>
+      <c r="AC118" s="8" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="n"/>
@@ -5861,6 +6010,7 @@
       <c r="Z119" s="9" t="n"/>
       <c r="AA119" s="35" t="n"/>
       <c r="AB119" s="8" t="n"/>
+      <c r="AC119" s="8" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="8" t="n"/>
@@ -5891,6 +6041,7 @@
       <c r="Z120" s="9" t="n"/>
       <c r="AA120" s="35" t="n"/>
       <c r="AB120" s="8" t="n"/>
+      <c r="AC120" s="8" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="AB3:AB120">

--- a/willitboard_operadores.xlsx
+++ b/willitboard_operadores.xlsx
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>LowFare+</t>
+          <t>LowFare+ or Flex ticket</t>
         </is>
       </c>
       <c r="N14" s="8" t="n">
@@ -2497,7 +2497,7 @@
       <c r="X14" s="8" t="n"/>
       <c r="Y14" s="8" t="inlineStr">
         <is>
-          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. PESO COMBINADO (columna peso_combinado_kg, 26/09/2026): LowFare incluye solo el bolso bajo el asiento (30x40x20 cm, máx. 10 kg). LowFare+ suma la valija 55x40x23 cm con PESO COMBINADO de 10 kg para los dos bultos; Flex, 15 kg combinados. El esquema guarda peso por bulto: dejar cabina_kg vacío haría que la ficha diga "sin límite de peso publicado", que es falso. [NO SÉ] ruedas/asas. Se carga peso_combinado_kg = 10 (LowFare+) y personal_kg = 10 (LowFare). Flex, 15 kg combinados: no se modela porque la fila describe LowFare.</t>
+          <t>Verificado por Marcos el 26/09/2026 con capturas de la página oficial: LowFare = solo el bolso bajo el asiento (30x40x20cm), 'Max weight limit 10 kg'; LowFare+ = bolso + 'Overhead cabin bag (55x40x23cm)', 'Combined weight limit of 10 kg'; Flex = 'Combined weight limit of 15 kg' (no se modela: la fila describe LowFare/LowFare+). 'If you're travelling on a LowFare+ or Flex ticket, you can also bring one overhead cabin bag.' RUEDAS Y ASAS: el texto no lo dice. El asistente revisó también la versión /en/ de la página el 26/09/2026: sin mención. El dibujo muestra la flecha de 55 cm de punta a punta, pero un dibujo no es una regla escrita: incluye_ruedas_manijas queda vacío y la ficha dice que no se sabe.</t>
         </is>
       </c>
       <c r="Z14" s="9" t="inlineStr">
@@ -2505,7 +2505,9 @@
           <t>https://www.norwegian.com/us/travel-info/baggage/hand-baggage/</t>
         </is>
       </c>
-      <c r="AA14" s="35" t="n"/>
+      <c r="AA14" s="35" t="n">
+        <v>46291</v>
+      </c>
       <c r="AB14" s="8" t="inlineStr">
         <is>
           <t>LowFare</t>
@@ -2594,7 +2596,7 @@
       <c r="X15" s="8" t="n"/>
       <c r="Y15" s="8" t="inlineStr">
         <is>
-          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. PESO COMBINADO (columna peso_combinado_kg, 26/09/2026): en Economy el peso es COMBINADO, 12 kg entre la valija y el bolso pequeño. Bolso pequeño 40x30x15 cm; valija 55x35x25 cm "including pockets, wheels, and handles". Las tarifas Basic incluyen solo el bolso pequeño; la valija requiere Flying Blue Gold+ o comprar la opción. Confirmar el nombre exacto de la tarifa (Basic o Light) y del extra. Se carga peso_combinado_kg = 12; los pesos por bulto quedan vacíos porque Air France no los publica por separado.</t>
+          <t>Verificado por Marcos el 26/09/2026 con capturas. El enlace wwws.airfrance.fr/en lo llevó a airfrance.dk (Dinamarca - EN), misma página. Textos: 'In the Economy cabin, 0 to 1 hand baggage depending on the fare chosen + 1 small bag (maximum total weight: 12 kg/26.4 lb.)'; small bag '40 x 30 x 15 cm'; hand baggage '55 x 35 x 25 cm (21.7 x 13.8 x 9.9 in.), including pockets, wheels, and handles'; 'Are you traveling with a Basic fare and would like to bring a hand baggage item in addition to your small bag?' -&gt; Flying Blue Gold o superior la lleva gratis; el resto 'can purchase the Hand Baggage option'. Pesos por bulto vacíos: Air France solo publica el total.</t>
         </is>
       </c>
       <c r="Z15" s="9" t="inlineStr">
@@ -2602,7 +2604,9 @@
           <t>https://wwws.airfrance.fr/en/information/bagages/bagage-cabine-soute</t>
         </is>
       </c>
-      <c r="AA15" s="35" t="n"/>
+      <c r="AA15" s="35" t="n">
+        <v>46291</v>
+      </c>
       <c r="AB15" s="8" t="inlineStr">
         <is>
           <t>Basic</t>
@@ -2663,7 +2667,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M16" s="8" t="n"/>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>1 piece of hand baggage (via My Trip)</t>
+        </is>
+      </c>
       <c r="N16" s="8" t="n">
         <v>55</v>
       </c>
@@ -2687,7 +2695,7 @@
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="8" t="inlineStr">
         <is>
-          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. PESO COMBINADO (columna peso_combinado_kg, 26/09/2026): peso COMBINADO de 12 kg entre bolso pequeño y valija en Economy. Bolso pequeño 40x30x15 cm bajo el asiento; valija 55x35x25 cm "including handles and wheels". Economy Light, Standard y Flex incluyen la valija; Basic solo el bolso pequeño. [NO SÉ] nombre del extra. Se carga peso_combinado_kg = 12; pesos por bulto vacíos.</t>
+          <t>Verificado por Marcos el 26/09/2026 con capturas (página en inglés que Chrome le tradujo al español). Texto original en inglés confirmado por el asistente el 26/09/2026 en la misma URL: 'If you have a Basic ticket, you're always allowed to bring 1 small bag with a maximum size of 40 x 30 x 15 cm.'; 'You can purchase 1 piece of hand baggage via My Trip up to 4 hours before your flight departs.'; 'Your small bag and hand baggage combined may weigh up to 12 kg.'; 'Your hand baggage, including handles and wheels, must not exceed the maximum size of 55 x 35 x 25 cm.' Light, Standard y Flex incluyen la valija. tarifa_referencia pasó de 'Economy Basic' a 'Basic', como lo escribe KLM.</t>
         </is>
       </c>
       <c r="Z16" s="9" t="inlineStr">
@@ -2695,10 +2703,12 @@
           <t>https://www.klm.nl/en/information/baggage/hand-baggage-allowance</t>
         </is>
       </c>
-      <c r="AA16" s="35" t="n"/>
+      <c r="AA16" s="35" t="n">
+        <v>46291</v>
+      </c>
       <c r="AB16" s="8" t="inlineStr">
         <is>
-          <t>Economy Basic</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="AC16" s="8" t="n">
@@ -2760,7 +2770,7 @@
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t>Smart fare, or cabin bag bought separately</t>
+          <t>Smart or Max fare, or a cabin bag added for a fee</t>
         </is>
       </c>
       <c r="N17" s="8" t="n">
@@ -2786,7 +2796,7 @@
       <c r="X17" s="8" t="n"/>
       <c r="Y17" s="8" t="inlineStr">
         <is>
-          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. PESO COMBINADO (columna peso_combinado_kg, 26/09/2026): bolso pequeño 40x30x20 cm y hasta 10 kg; con valija 55x40x25 cm el PESO ES COMBINADO, 10 kg entre los dos. Medidas "including wheels and handles". Basic y Plus no incluyen la valija; Smart y Max sí, con Priority Boarding. cabina_addon es descripción del asistente: confirmar el nombre comercial. Se carga personal_kg = 10 y peso_combinado_kg = 10.</t>
+          <t>Verificado por Marcos el 26/09/2026 con captura: bolso 'max. 40 x 30 x 20 cm', 'The maximum allowed weight for your hand luggage is 10 kg'; valija 'max. 55 x 40 x 25 cm' 'for a fee'; 'Your hand luggage and cabin bag combined may weigh up to 10 kg'; 'If you have booked the Smart or Max fare, then your fare includes a cabin bag and Priority Boarding.' Confirmado por el asistente el 26/09/2026: la nota (*) de la misma página dice 'The measurements include the wheels and handles.'; el nombre de la tarifa base, 'Basic fare', sale de https://www.transavia.com/help/en-eu/search-and-book/basic-smart-plus-max-fare/basic-fare ('One piece of hand luggage of maximum 40 x 30 x 20 cm').</t>
         </is>
       </c>
       <c r="Z17" s="9" t="inlineStr">
@@ -2794,7 +2804,9 @@
           <t>https://www.transavia.com/help/en-eu/baggage/cabin-baggage/how-much-to-bring</t>
         </is>
       </c>
-      <c r="AA17" s="35" t="n"/>
+      <c r="AA17" s="35" t="n">
+        <v>46291</v>
+      </c>
       <c r="AB17" s="8" t="inlineStr">
         <is>
           <t>Basic</t>

--- a/willitboard_operadores.xlsx
+++ b/willitboard_operadores.xlsx
@@ -2200,7 +2200,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M11" s="8" t="n"/>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>2 pieces on board service, or a Space One / Space Plus / Space seat</t>
+        </is>
+      </c>
       <c r="N11" s="8" t="n">
         <v>55</v>
       </c>
@@ -2222,7 +2226,7 @@
       <c r="X11" s="8" t="n"/>
       <c r="Y11" s="8" t="inlineStr">
         <is>
-          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. Bolso bajo el asiento 40x30x20 cm en todas las tarifas, sin peso publicado. Valija de compartimento 55x40x20 cm y 10 kg: incluida en Fly/Fly Grande/Fly Pro/Premium, de pago en Fly Light. [NO SÉ] nombre exacto del extra (cabina_addon vacío) y si las medidas incluyen ruedas y asas. Confirmar además el nombre de la tarifa base.</t>
+          <t>Verificado por Marcos el 26/09/2026 con capturas de la página oficial. Fly Light bundle: '1 free underseat cabin bag size (max. 40x30x20 cm)'; opción de valija en el compartimento '(max. 10 kg and 55x40x20 cm) by adding the 2 pieces on board service or choosing Space One, Space Plus or Space seats'. Fly, Fly Grande, Fly Pro y Premium la incluyen. Peso del bolso no publicado. Ruedas y asas: no lo dice; queda vacío.</t>
         </is>
       </c>
       <c r="Z11" s="9" t="inlineStr">
@@ -2230,7 +2234,9 @@
           <t>https://help.vueling.com/hc/en-gb/articles/19798835176081-Hand-Luggage-Allowance-Cabin-bags-allowance</t>
         </is>
       </c>
-      <c r="AA11" s="35" t="n"/>
+      <c r="AA11" s="35" t="n">
+        <v>46291</v>
+      </c>
       <c r="AB11" s="8" t="inlineStr">
         <is>
           <t>Fly Light</t>
@@ -2315,7 +2321,7 @@
       <c r="X12" s="8" t="n"/>
       <c r="Y12" s="8" t="inlineStr">
         <is>
-          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. Economy Basic incluye solo el artículo personal 40x30x15 cm; el equipaje de mano 55x40x23 cm y 8 kg no está incluido y se compra solo online, hasta 2 h antes. Economy Light, Comfort, Comfort Green y Flex lo incluyen. [NO SÉ] peso del artículo personal y si las medidas incluyen ruedas y asas. cabina_addon es descripción del asistente, no nombre comercial: confirmar cómo lo llama Lufthansa. La URL es la versión /ba/en/ que devolvió la búsqueda; si existe la misma página en /de/en/, citar esa.</t>
+          <t>Verificado por Marcos el 26/09/2026 con capturas de la página oficial. 'The fare includes one personal item (up to a maximum of 40 x 30 x 15 cm)'; 'the Economy Basic fare does not include a carry-on bag (8 kg, 55 x 40 x 23 cm)'; 'Carry-on baggage can only be purchased online and is not available at the airport', hasta 2 h antes. Peso del artículo personal no publicado. Ruedas y asas: no lo dice; queda vacío.</t>
         </is>
       </c>
       <c r="Z12" s="9" t="inlineStr">
@@ -2323,7 +2329,9 @@
           <t>https://www.lufthansa.com/ba/en/prepare-for-your-trip/travel-classes/economy-basic</t>
         </is>
       </c>
-      <c r="AA12" s="35" t="n"/>
+      <c r="AA12" s="35" t="n">
+        <v>46291</v>
+      </c>
       <c r="AB12" s="8" t="inlineStr">
         <is>
           <t>Economy Basic</t>
@@ -2382,7 +2390,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M13" s="8" t="n"/>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>Carry-on bag (Economy Light only)</t>
+        </is>
+      </c>
       <c r="N13" s="8" t="n">
         <v>55</v>
       </c>
@@ -2404,7 +2416,7 @@
       <c r="X13" s="8" t="n"/>
       <c r="Y13" s="8" t="inlineStr">
         <is>
-          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. Artículo personal 40x30x15 cm y capacidad máxima 18 L (dato que el esquema no guarda). Equipaje de cabina 55x40x23 cm, 8 kg: incluido en Economy Standard, Flex, Premium y Business; en Economy Light se puede comprar. [NO SÉ] peso del artículo personal, nombre del extra y ruedas/asas. Confirmar si la tarifa base hoy se llama Economy Light o SAS Go Light. pais = SE por SAS AB (Estocolmo).</t>
+          <t>Verificado por Marcos el 26/09/2026 con capturas de la página oficial. Underseat bag 'Max size: 40 x 30 x 15 cm', 'Max capacity: 18 L' (dato que el esquema no guarda); carry-on 'Max size: 55 x 40 x 23 cm', 'Max weight: 8 kg'; 'The purchase of a carry-on bag is only available for travelers with an Economy Light ticket'; Standard, Flex, Premium y Business ya la incluyen. Ruedas y asas: el texto no lo dice (Marcos cree por el dibujo que no las incluye); queda vacío.</t>
         </is>
       </c>
       <c r="Z13" s="9" t="inlineStr">
@@ -2412,7 +2424,9 @@
           <t>https://www.flysas.com/us-en/travel-info/baggage/carry-on</t>
         </is>
       </c>
-      <c r="AA13" s="35" t="n"/>
+      <c r="AA13" s="35" t="n">
+        <v>46291</v>
+      </c>
       <c r="AB13" s="8" t="inlineStr">
         <is>
           <t>Economy Light</t>
@@ -2847,7 +2861,11 @@
           <t>dimensional</t>
         </is>
       </c>
-      <c r="G18" s="8" t="n"/>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="H18" s="8" t="n">
         <v>40</v>
       </c>
@@ -2858,7 +2876,11 @@
         <v>15</v>
       </c>
       <c r="K18" s="8" t="n"/>
-      <c r="L18" s="8" t="n"/>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="M18" s="8" t="n"/>
       <c r="N18" s="8" t="n">
         <v>56</v>
@@ -2881,15 +2903,17 @@
       <c r="X18" s="8" t="n"/>
       <c r="Y18" s="8" t="inlineStr">
         <is>
-          <t>CANDIDATA 24/09/2026, SIN FECHA A PROPÓSITO: el conversor la omite hasta que Marcos confirme en la fuente. Cifras leídas por el asistente con una herramienta de resumen [SIN VERIFICAR] — confirmar cada una contra la página. FUENTE DÉBIL: iberia.com devolvió error (redirecciones y 404) y las cifras salen del portal de AGENCIAS de Iberia: equipaje de mano 56x40x25 cm y 10 kg en Economy, artículo personal 30x40x15 cm. Hace falta la página pública de iberia.com para publicar. [NO SÉ] si la tarifa Basic incluye la valija (personal_incluido y cabina_incluida vacíos a propósito), peso del artículo personal y ruedas/asas.</t>
+          <t>Verificado por Marcos el 26/09/2026 con capturas de la página oficial. Fuente cambiada a la página pública de iberia.com. 'En Iberia, todas nuestras tarifas incluyen un equipaje de hasta 10 Kg y un equipaje de mano personal gratuito'; Clase Turista: '1 equipaje de hasta 10 kg. 56 x 40 x 25 cm' y '1 equipaje de mano personal 30 x 40 x 15 cm' bajo el asiento. Como todas las tarifas incluyen lo mismo, tarifa_referencia queda vacía. Ruedas y asas: no lo dice; queda vacío.</t>
         </is>
       </c>
       <c r="Z18" s="9" t="inlineStr">
         <is>
-          <t>https://agencias.iberia.com/content/iberia-agencias/language-masters/en/informacion-viaje/equipajes/hand-baggage.html</t>
-        </is>
-      </c>
-      <c r="AA18" s="35" t="n"/>
+          <t>https://www.iberia.com/es/equipajes/de-mano/</t>
+        </is>
+      </c>
+      <c r="AA18" s="35" t="n">
+        <v>46291</v>
+      </c>
       <c r="AB18" s="8" t="n"/>
       <c r="AC18" s="8" t="n"/>
     </row>

--- a/willitboard_operadores.xlsx
+++ b/willitboard_operadores.xlsx
@@ -2918,54 +2918,166 @@
       <c r="AC18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n"/>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>aer-lingus</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Aer Lingus</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>20</v>
+      </c>
       <c r="K19" s="8" t="n"/>
-      <c r="L19" s="8" t="n"/>
-      <c r="M19" s="8" t="n"/>
-      <c r="N19" s="8" t="n"/>
-      <c r="O19" s="8" t="n"/>
-      <c r="P19" s="8" t="n"/>
-      <c r="Q19" s="8" t="n"/>
-      <c r="R19" s="8" t="n"/>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>10kg Carry-on bag</t>
+        </is>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="P19" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="S19" s="33" t="n"/>
       <c r="T19" s="8" t="n"/>
       <c r="U19" s="8" t="n"/>
       <c r="V19" s="8" t="n"/>
       <c r="W19" s="8" t="n"/>
       <c r="X19" s="8" t="n"/>
-      <c r="Y19" s="8" t="n"/>
-      <c r="Z19" s="9" t="n"/>
+      <c r="Y19" s="8" t="inlineStr">
+        <is>
+          <t>[SIN VERIFICAR] Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. Página: 'Carry-on baggage must fit inside the gauge units at the airport (including wheels and handles).' La valija de 10 kg viene en Plus, Advantage, Aer Space y socios AerClub Silver+; en la tarifa base se compra. Falta: nombre exacto de la tarifa base (¿Saver?) y del extra. La URL /prepare/bags/carry-on-baggage/ devolvió 405 a la herramienta; se leyó el modal /localized/en/modals/baggage-information.html.</t>
+        </is>
+      </c>
+      <c r="Z19" s="9" t="inlineStr">
+        <is>
+          <t>https://www.aerlingus.com/prepare/bags/carry-on-baggage/</t>
+        </is>
+      </c>
       <c r="AA19" s="35" t="n"/>
       <c r="AB19" s="8" t="n"/>
       <c r="AC19" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n"/>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>eurowings</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Eurowings</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>25</v>
+      </c>
       <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n"/>
-      <c r="N20" s="8" t="n"/>
-      <c r="O20" s="8" t="n"/>
-      <c r="P20" s="8" t="n"/>
-      <c r="Q20" s="8" t="n"/>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>Large hand luggage</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="P20" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q20" s="8" t="n">
+        <v>8</v>
+      </c>
       <c r="R20" s="8" t="n"/>
       <c r="S20" s="33" t="n"/>
       <c r="T20" s="8" t="n"/>
@@ -2973,30 +3085,90 @@
       <c r="V20" s="8" t="n"/>
       <c r="W20" s="8" t="n"/>
       <c r="X20" s="8" t="n"/>
-      <c r="Y20" s="8" t="n"/>
-      <c r="Z20" s="9" t="n"/>
+      <c r="Y20" s="8" t="inlineStr">
+        <is>
+          <t>[SIN VERIFICAR] Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. Personal 40x30x25 en todas las tarifas. Valija 55x40x23 hasta 8 kg: incluida en SMART y BIZclass; en BASIC se paga (desde 18 EUR / 16 GBP según la herramienta, NO cargado). Ruedas y asas: la herramienta no encontró mención. Confirmar nombre exacto del extra.</t>
+        </is>
+      </c>
+      <c r="Z20" s="9" t="inlineStr">
+        <is>
+          <t>https://www.eurowings.com/en/information/baggage/hand-baggage-policy.html</t>
+        </is>
+      </c>
       <c r="AA20" s="35" t="n"/>
-      <c r="AB20" s="8" t="n"/>
+      <c r="AB20" s="8" t="inlineStr">
+        <is>
+          <t>BASIC</t>
+        </is>
+      </c>
       <c r="AC20" s="8" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="8" t="n"/>
-      <c r="L21" s="8" t="n"/>
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>tap-air-portugal</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>TAP Air Portugal</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="M21" s="8" t="n"/>
-      <c r="N21" s="8" t="n"/>
-      <c r="O21" s="8" t="n"/>
-      <c r="P21" s="8" t="n"/>
-      <c r="Q21" s="8" t="n"/>
+      <c r="N21" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q21" s="8" t="n">
+        <v>10</v>
+      </c>
       <c r="R21" s="8" t="n"/>
       <c r="S21" s="33" t="n"/>
       <c r="T21" s="8" t="n"/>
@@ -3004,101 +3176,279 @@
       <c r="V21" s="8" t="n"/>
       <c r="W21" s="8" t="n"/>
       <c r="X21" s="8" t="n"/>
-      <c r="Y21" s="8" t="n"/>
-      <c r="Z21" s="9" t="n"/>
+      <c r="Y21" s="8" t="inlineStr">
+        <is>
+          <t>[SIN VERIFICAR] Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. Página: 'When travelling with TAP, you can take hand baggage and a personal item free of charge.' Valija 55x40x25 / 10 kg; personal 40x30x15 / 2 kg. Confirmar que vale también para la tarifa más barata en Europa (Discount) y si las medidas incluyen ruedas y asas (la herramienta no lo encontró).</t>
+        </is>
+      </c>
+      <c r="Z21" s="9" t="inlineStr">
+        <is>
+          <t>https://www.flytap.com/en-pt/baggage/hand-baggage</t>
+        </is>
+      </c>
       <c r="AA21" s="35" t="n"/>
       <c r="AB21" s="8" t="n"/>
       <c r="AC21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n"/>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>jet2</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Jet2</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>20</v>
+      </c>
       <c r="K22" s="8" t="n"/>
-      <c r="L22" s="8" t="n"/>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="M22" s="8" t="n"/>
-      <c r="N22" s="8" t="n"/>
-      <c r="O22" s="8" t="n"/>
-      <c r="P22" s="8" t="n"/>
-      <c r="Q22" s="8" t="n"/>
-      <c r="R22" s="8" t="n"/>
+      <c r="N22" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q22" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="S22" s="33" t="n"/>
       <c r="T22" s="8" t="n"/>
       <c r="U22" s="8" t="n"/>
       <c r="V22" s="8" t="n"/>
       <c r="W22" s="8" t="n"/>
       <c r="X22" s="8" t="n"/>
-      <c r="Y22" s="8" t="n"/>
-      <c r="Z22" s="9" t="n"/>
+      <c r="Y22" s="8" t="inlineStr">
+        <is>
+          <t>[SIN VERIFICAR] Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. Página: '10kg hand luggage allowance included as standard (excluding infants) which must be no larger than 56cm x 45cm x 25cm (including wheels and handles)' y 'one small under-seat bag ... must not exceed 40 x 30 x 20cm'. Bolso sin peso publicado. Segundo caso tipo BA: todo incluido.</t>
+        </is>
+      </c>
+      <c r="Z22" s="9" t="inlineStr">
+        <is>
+          <t>https://www.jet2.com/en/baggage</t>
+        </is>
+      </c>
       <c r="AA22" s="35" t="n"/>
       <c r="AB22" s="8" t="n"/>
       <c r="AC22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n"/>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="8" t="n"/>
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>sncf-tgv-inoui</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>TGV INOUI (SNCF)</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="K23" s="8" t="n"/>
-      <c r="L23" s="8" t="n"/>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="M23" s="8" t="n"/>
-      <c r="N23" s="8" t="n"/>
-      <c r="O23" s="8" t="n"/>
-      <c r="P23" s="8" t="n"/>
+      <c r="N23" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="P23" s="8" t="n">
+        <v>50</v>
+      </c>
       <c r="Q23" s="8" t="n"/>
       <c r="R23" s="8" t="n"/>
       <c r="S23" s="33" t="n"/>
-      <c r="T23" s="8" t="n"/>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
       <c r="U23" s="8" t="n"/>
       <c r="V23" s="8" t="n"/>
       <c r="W23" s="8" t="n"/>
       <c r="X23" s="8" t="n"/>
-      <c r="Y23" s="8" t="n"/>
-      <c r="Z23" s="9" t="n"/>
+      <c r="Y23" s="8" t="inlineStr">
+        <is>
+          <t>[SIN VERIFICAR] Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. PRIMER TREN DIMENSIONAL. '2 suitcases + 1 item of hand luggage'; 'hand luggage ... maximum of 40 cm x 30 cm x 15 cm'; 'suitcase ... maximum of 70 cm x 90 cm x 50 cm'. Multa 50/100/150 EUR por bultos de más o fuera de medida (NO cargada en tarifas). Vale también para Intercités según la página. OJO ANTES DE PUBLICAR: las etiquetas del sitio dicen 'personal item' / 'cabin bag'; para un tren hay que mostrar 'hand luggage' / 'suitcase' (cambio chico en build_site y diccionarios).</t>
+        </is>
+      </c>
+      <c r="Z23" s="9" t="inlineStr">
+        <is>
+          <t>https://www.sncf-connect.com/en-en/help/transport-luggage</t>
+        </is>
+      </c>
       <c r="AA23" s="35" t="n"/>
       <c r="AB23" s="8" t="n"/>
       <c r="AC23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n"/>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>ouigo</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>OUIGO</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="K24" s="8" t="n"/>
-      <c r="L24" s="8" t="n"/>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="M24" s="8" t="n"/>
-      <c r="N24" s="8" t="n"/>
-      <c r="O24" s="8" t="n"/>
-      <c r="P24" s="8" t="n"/>
+      <c r="N24" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="P24" s="8" t="n">
+        <v>25</v>
+      </c>
       <c r="Q24" s="8" t="n"/>
       <c r="R24" s="8" t="n"/>
       <c r="S24" s="33" t="n"/>
-      <c r="T24" s="8" t="n"/>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
       <c r="U24" s="8" t="n"/>
       <c r="V24" s="8" t="n"/>
       <c r="W24" s="8" t="n"/>
       <c r="X24" s="8" t="n"/>
-      <c r="Y24" s="8" t="n"/>
-      <c r="Z24" s="9" t="n"/>
+      <c r="Y24" s="8" t="inlineStr">
+        <is>
+          <t>[SIN VERIFICAR] Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. OUIGO Francia (no OUIGO España, que tiene otras reglas). 'one item of cabin luggage (55 x 35 x 25 cm)' y 'one item of hand luggage (40 x 30 x 15 cm)'. Bulto extra o voluminoso hasta 130x90x50 y 30 kg: 5 EUR al reservar, 20 EUR en el lugar (NO cargado). Confirmar que las dos piezas van incluidas en el billete básico. Misma advertencia de etiquetas que TGV INOUI.</t>
+        </is>
+      </c>
+      <c r="Z24" s="9" t="inlineStr">
+        <is>
+          <t>https://www.sncf-connect.com/en-en/help/transport-luggage</t>
+        </is>
+      </c>
       <c r="AA24" s="35" t="n"/>
       <c r="AB24" s="8" t="n"/>
       <c r="AC24" s="8" t="n"/>

--- a/willitboard_operadores.xlsx
+++ b/willitboard_operadores.xlsx
@@ -3454,54 +3454,170 @@
       <c r="AC24" s="8" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n"/>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="8" t="n"/>
-      <c r="K25" s="8" t="n"/>
-      <c r="L25" s="8" t="n"/>
-      <c r="M25" s="8" t="n"/>
-      <c r="N25" s="8" t="n"/>
-      <c r="O25" s="8" t="n"/>
-      <c r="P25" s="8" t="n"/>
-      <c r="Q25" s="8" t="n"/>
-      <c r="R25" s="8" t="n"/>
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>jetsmart</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>JetSMART</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>LATAM</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>Equipaje de mano</t>
+        </is>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="S25" s="33" t="n"/>
       <c r="T25" s="8" t="n"/>
       <c r="U25" s="8" t="n"/>
       <c r="V25" s="8" t="n"/>
       <c r="W25" s="8" t="n"/>
       <c r="X25" s="8" t="n"/>
-      <c r="Y25" s="8" t="n"/>
-      <c r="Z25" s="9" t="n"/>
-      <c r="AA25" s="35" t="n"/>
+      <c r="Y25" s="8" t="inlineStr">
+        <is>
+          <t>Verificado por Marcos el 03/10/2026 con capturas de la página oficial jetsmart.com/cl/es/opcionales (Opcionales - Condiciones y Precios). Bolso o Mochila pequeña: 'No puede exceder los 10 Kg ni las siguientes dimensiones: 45cm x 35cm x 25cm (largo, ancho, alto), incluyendo ruedas, asas y bolsillos'; 'puedes llevar sin costo un porta notebook, porta traje o pañalera'; bajo el asiento delantero. Equipaje de mano: 'No puede exceder los 10 Kg ni las siguientes dimensiones: 55cm x 35cm x 25cm (largo, ancho, alto), incluyendo ruedas, asas y bolsillos'; compartimientos superiores; 'Límite de una unidad por pasajero'. Es un opcional que se compra (página de Opcionales); precio no cargado. Marcos confirmó que las medidas son las mismas en Chile, Argentina y Perú. Nombre de la tarifa base: no encontrado, tarifa_referencia vacía.</t>
+        </is>
+      </c>
+      <c r="Z25" s="9" t="inlineStr">
+        <is>
+          <t>https://jetsmart.com/cl/es/opcionales</t>
+        </is>
+      </c>
+      <c r="AA25" s="35" t="n">
+        <v>46298</v>
+      </c>
       <c r="AB25" s="8" t="n"/>
       <c r="AC25" s="8" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n"/>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n"/>
-      <c r="J26" s="8" t="n"/>
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>volaris</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Volaris</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>LATAM</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="J26" s="8" t="n">
+        <v>20</v>
+      </c>
       <c r="K26" s="8" t="n"/>
-      <c r="L26" s="8" t="n"/>
-      <c r="M26" s="8" t="n"/>
-      <c r="N26" s="8" t="n"/>
-      <c r="O26" s="8" t="n"/>
-      <c r="P26" s="8" t="n"/>
-      <c r="Q26" s="8" t="n"/>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>Equipaje de mano</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="P26" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q26" s="8" t="n">
+        <v>10</v>
+      </c>
       <c r="R26" s="8" t="n"/>
       <c r="S26" s="33" t="n"/>
       <c r="T26" s="8" t="n"/>
@@ -3509,30 +3625,90 @@
       <c r="V26" s="8" t="n"/>
       <c r="W26" s="8" t="n"/>
       <c r="X26" s="8" t="n"/>
-      <c r="Y26" s="8" t="n"/>
-      <c r="Z26" s="9" t="n"/>
-      <c r="AA26" s="35" t="n"/>
-      <c r="AB26" s="8" t="n"/>
-      <c r="AC26" s="8" t="n"/>
+      <c r="Y26" s="8" t="inlineStr">
+        <is>
+          <t>Verificado por Marcos el 03/10/2026 con capturas de la página oficial. Tarifas Zero, Básica y Plus. Objeto personal en las tres, 'Sus dimensiones máximas son 35 × 45 × 20 cm', sin peso propio publicado. Equipaje de mano '55 × 40 × 25 cm (largo × ancho × alto) y un peso máximo de 10 kg': solo incluido en Plus; Zero: 'El equipaje de mano y documentado no están incluidos en esta opción'; Básica: 'El equipaje de mano no está incluido en esta opción'. 'El peso total del equipaje de mano y el artículo personal no debe exceder los 20 kg en conjunto' (peso_combinado_kg). 'Las medidas y pesos indicados a continuación aplican para vuelos nacionales e internacionales.' Ruedas y asas: no lo dice; queda vacío.</t>
+        </is>
+      </c>
+      <c r="Z26" s="9" t="inlineStr">
+        <is>
+          <t>https://cms.volaris.com/es/informacion-util/politicas-de-equipaje/</t>
+        </is>
+      </c>
+      <c r="AA26" s="35" t="n">
+        <v>46298</v>
+      </c>
+      <c r="AB26" s="8" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+      <c r="AC26" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n"/>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="8" t="n"/>
-      <c r="K27" s="8" t="n"/>
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>latam</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>LATAM Airlines</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>LATAM</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="K27" s="8" t="n">
+        <v>10</v>
+      </c>
       <c r="L27" s="8" t="n"/>
       <c r="M27" s="8" t="n"/>
-      <c r="N27" s="8" t="n"/>
-      <c r="O27" s="8" t="n"/>
-      <c r="P27" s="8" t="n"/>
-      <c r="Q27" s="8" t="n"/>
+      <c r="N27" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="P27" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q27" s="8" t="n">
+        <v>12</v>
+      </c>
       <c r="R27" s="8" t="n"/>
       <c r="S27" s="33" t="n"/>
       <c r="T27" s="8" t="n"/>
@@ -3540,41 +3716,117 @@
       <c r="V27" s="8" t="n"/>
       <c r="W27" s="8" t="n"/>
       <c r="X27" s="8" t="n"/>
-      <c r="Y27" s="8" t="n"/>
-      <c r="Z27" s="9" t="n"/>
+      <c r="Y27" s="8" t="inlineStr">
+        <is>
+          <t>[PENDIENTE] Captura de Marcos del 03/10/2026, página /co/es/centro-ayuda/preguntas/equipaje/incluido/dimensiones-peso. Bolso o mochila pequeña: 'El peso máximo es de 10 kg (22 lb)'; 'Las medidas máximas son de 45 x 35 x 20 cm (alto x largo x ancho), incluyendo los bolsillos, las ruedas, el asa, etc.'. Equipaje de mano: 'El peso máximo es de 12 kg (26 lb) si viajas en cabina Economy y 16 kg (35 lb) si viajas en cabina Premium Economy o Premium Business'; 'Las medidas máximas de este equipaje son de 55 cm alto + 35 cm largo + 25 cm ancho' (no menciona ruedas para la maleta: incluye_ruedas_manijas queda vacío). FALTA para publicar: qué tarifas incluyen el equipaje de mano (cabina_incluida y tarifa_referencia). Sin fecha hasta tenerlo.</t>
+        </is>
+      </c>
+      <c r="Z27" s="9" t="inlineStr">
+        <is>
+          <t>https://www.latamairlines.com/co/es/centro-ayuda/preguntas/equipaje/incluido/dimensiones-peso</t>
+        </is>
+      </c>
       <c r="AA27" s="35" t="n"/>
       <c r="AB27" s="8" t="n"/>
       <c r="AC27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n"/>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
-      <c r="J28" s="8" t="n"/>
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>avianca</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Avianca</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>LATAM</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="I28" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>20</v>
+      </c>
       <c r="K28" s="8" t="n"/>
-      <c r="L28" s="8" t="n"/>
-      <c r="M28" s="8" t="n"/>
-      <c r="N28" s="8" t="n"/>
-      <c r="O28" s="8" t="n"/>
-      <c r="P28" s="8" t="n"/>
-      <c r="Q28" s="8" t="n"/>
-      <c r="R28" s="8" t="n"/>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>Equipaje de mano</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O28" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q28" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="S28" s="33" t="n"/>
       <c r="T28" s="8" t="n"/>
       <c r="U28" s="8" t="n"/>
       <c r="V28" s="8" t="n"/>
       <c r="W28" s="8" t="n"/>
       <c r="X28" s="8" t="n"/>
-      <c r="Y28" s="8" t="n"/>
-      <c r="Z28" s="9" t="n"/>
-      <c r="AA28" s="35" t="n"/>
-      <c r="AB28" s="8" t="n"/>
+      <c r="Y28" s="8" t="inlineStr">
+        <is>
+          <t>Verificado por Marcos el 03/10/2026 con capturas de avianca.com/es/mi-reserva/prepara-tu-viaje/equipaje y de avianca.com/es/experiencia-avianca/clases-y-tarifas/tipos-de-tarifas. Artículo personal: 'Medidas máximas: 45 × 35 × 20 cm (alto, largo y ancho)', bajo el asiento, 'En todas nuestras tarifas podrás llevar un artículo personal gratis'; sin peso publicado. Equipaje de mano: 'Medidas máximas: 55 x 35 x 25 cm (alto, largo y ancho), incluyendo ruedas y manijas'; 'Peso máximo: 10 kg'; 'Incluido en todas las tarifas a excepción de la tarifa Basic'. La tarifa Basic lleva la etiqueta 'Vuelos nacionales'; en internacionales la más barata es Light, que SÍ incluye el equipaje de mano. Referencia elegida: Basic (la más barata). Precio del extra no cargado.</t>
+        </is>
+      </c>
+      <c r="Z28" s="9" t="inlineStr">
+        <is>
+          <t>https://www.avianca.com/es/mi-reserva/prepara-tu-viaje/equipaje</t>
+        </is>
+      </c>
+      <c r="AA28" s="35" t="n">
+        <v>46298</v>
+      </c>
+      <c r="AB28" s="8" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
       <c r="AC28" s="8" t="n"/>
     </row>
     <row r="29">

--- a/willitboard_operadores.xlsx
+++ b/willitboard_operadores.xlsx
@@ -3695,8 +3695,16 @@
       <c r="K27" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="L27" s="8" t="n"/>
-      <c r="M27" s="8" t="n"/>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t>Equipaje de mano</t>
+        </is>
+      </c>
       <c r="N27" s="8" t="n">
         <v>55</v>
       </c>
@@ -3718,7 +3726,7 @@
       <c r="X27" s="8" t="n"/>
       <c r="Y27" s="8" t="inlineStr">
         <is>
-          <t>[PENDIENTE] Captura de Marcos del 03/10/2026, página /co/es/centro-ayuda/preguntas/equipaje/incluido/dimensiones-peso. Bolso o mochila pequeña: 'El peso máximo es de 10 kg (22 lb)'; 'Las medidas máximas son de 45 x 35 x 20 cm (alto x largo x ancho), incluyendo los bolsillos, las ruedas, el asa, etc.'. Equipaje de mano: 'El peso máximo es de 12 kg (26 lb) si viajas en cabina Economy y 16 kg (35 lb) si viajas en cabina Premium Economy o Premium Business'; 'Las medidas máximas de este equipaje son de 55 cm alto + 35 cm largo + 25 cm ancho' (no menciona ruedas para la maleta: incluye_ruedas_manijas queda vacío). FALTA para publicar: qué tarifas incluyen el equipaje de mano (cabina_incluida y tarifa_referencia). Sin fecha hasta tenerlo.</t>
+          <t>[PENDIENTE] Captura de Marcos del 03/10/2026, página /co/es/centro-ayuda/preguntas/equipaje/incluido/dimensiones-peso. Bolso o mochila pequeña: 'El peso máximo es de 10 kg (22 lb)'; 'Las medidas máximas son de 45 x 35 x 20 cm (alto x largo x ancho), incluyendo los bolsillos, las ruedas, el asa, etc.'. Equipaje de mano: 'El peso máximo es de 12 kg (26 lb) si viajas en cabina Economy y 16 kg (35 lb) si viajas en cabina Premium Economy o Premium Business'; 'Las medidas máximas de este equipaje son de 55 cm alto + 35 cm largo + 25 cm ancho' (no menciona ruedas para la maleta: incluye_ruedas_manijas queda vacío). [CANDIDATO, preparado por el asistente el 03/10/2026, SIN VERIFICAR por Marcos] Tabla oficial de tarifas latamairlines.com/co/es/centro-ayuda/preguntas/compras/asistencia/tarifas-pasaje-domestico (cabinas Economy): 'Equipaje de mano de 12 kg': Basic 'Con costo extra', Light '1 pieza', Full '1 pieza'. Restricción: Basic disponible en rutas domésticas de Chile, Colombia, Ecuador y Perú, además de Caribe y rutas regionales que no salgan de Brasil; no aplica a vuelos domésticos de Brasil. Referencia elegida: Basic (la más barata), mismo criterio que Avianca. OJO: la página en inglés /us/en/help-center/faq/purchases/asistance/ticket-fares habla de 'a 10 kg suitcase' en Basic; contradice los 12 kg de dimensiones-peso y de la tabla de tarifas. Se usa 12 kg (dos páginas oficiales coinciden).</t>
         </is>
       </c>
       <c r="Z27" s="9" t="inlineStr">
@@ -3727,7 +3735,11 @@
         </is>
       </c>
       <c r="AA27" s="35" t="n"/>
-      <c r="AB27" s="8" t="n"/>
+      <c r="AB27" s="8" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
       <c r="AC27" s="8" t="n"/>
     </row>
     <row r="28">

--- a/willitboard_operadores.xlsx
+++ b/willitboard_operadores.xlsx
@@ -3726,7 +3726,7 @@
       <c r="X27" s="8" t="n"/>
       <c r="Y27" s="8" t="inlineStr">
         <is>
-          <t>[PENDIENTE] Captura de Marcos del 03/10/2026, página /co/es/centro-ayuda/preguntas/equipaje/incluido/dimensiones-peso. Bolso o mochila pequeña: 'El peso máximo es de 10 kg (22 lb)'; 'Las medidas máximas son de 45 x 35 x 20 cm (alto x largo x ancho), incluyendo los bolsillos, las ruedas, el asa, etc.'. Equipaje de mano: 'El peso máximo es de 12 kg (26 lb) si viajas en cabina Economy y 16 kg (35 lb) si viajas en cabina Premium Economy o Premium Business'; 'Las medidas máximas de este equipaje son de 55 cm alto + 35 cm largo + 25 cm ancho' (no menciona ruedas para la maleta: incluye_ruedas_manijas queda vacío). [CANDIDATO, preparado por el asistente el 03/10/2026, SIN VERIFICAR por Marcos] Tabla oficial de tarifas latamairlines.com/co/es/centro-ayuda/preguntas/compras/asistencia/tarifas-pasaje-domestico (cabinas Economy): 'Equipaje de mano de 12 kg': Basic 'Con costo extra', Light '1 pieza', Full '1 pieza'. Restricción: Basic disponible en rutas domésticas de Chile, Colombia, Ecuador y Perú, además de Caribe y rutas regionales que no salgan de Brasil; no aplica a vuelos domésticos de Brasil. Referencia elegida: Basic (la más barata), mismo criterio que Avianca. OJO: la página en inglés /us/en/help-center/faq/purchases/asistance/ticket-fares habla de 'a 10 kg suitcase' en Basic; contradice los 12 kg de dimensiones-peso y de la tabla de tarifas. Se usa 12 kg (dos páginas oficiales coinciden).</t>
+          <t>Verificado por Marcos el 03/10/2026 con capturas, página /co/es/centro-ayuda/preguntas/equipaje/incluido/dimensiones-peso. Bolso o mochila pequeña: 'El peso máximo es de 10 kg (22 lb)'; 'Las medidas máximas son de 45 x 35 x 20 cm (alto x largo x ancho), incluyendo los bolsillos, las ruedas, el asa, etc.'. Equipaje de mano: 'El peso máximo es de 12 kg (26 lb) si viajas en cabina Economy y 16 kg (35 lb) si viajas en cabina Premium Economy o Premium Business'; 'Las medidas máximas de este equipaje son de 55 cm alto + 35 cm largo + 25 cm ancho' (no menciona ruedas para la maleta: incluye_ruedas_manijas queda vacío). Tabla oficial (confirmada por Marcos con captura el 03/10/2026) de tarifas latamairlines.com/co/es/centro-ayuda/preguntas/compras/asistencia/tarifas-pasaje-domestico (cabinas Economy): 'Equipaje de mano de 12 kg': Basic 'Con costo extra', Light '1 pieza', Full '1 pieza'. Restricción: Basic disponible en rutas domésticas de Chile, Colombia, Ecuador y Perú, además de Caribe y rutas regionales que no salgan de Brasil; no aplica a vuelos domésticos de Brasil. Referencia elegida: Basic (la más barata), mismo criterio que Avianca. OJO: la página en inglés /us/en/help-center/faq/purchases/asistance/ticket-fares habla de 'a 10 kg suitcase' en Basic; contradice los 12 kg de dimensiones-peso y de la tabla de tarifas. Marcos eligió 12 kg el 03/10/2026. El asistente comprobó ese día que /cl/, /pe/ y /ec/ dimensiones-peso dicen lo mismo (12 kg Economy, 55 x 35 x 25) y que la tabla /cl/ de tarifas coincide (Basic 'Con costo extra', Light y Full '1 pieza').</t>
         </is>
       </c>
       <c r="Z27" s="9" t="inlineStr">
@@ -3734,7 +3734,9 @@
           <t>https://www.latamairlines.com/co/es/centro-ayuda/preguntas/equipaje/incluido/dimensiones-peso</t>
         </is>
       </c>
-      <c r="AA27" s="35" t="n"/>
+      <c r="AA27" s="35" t="n">
+        <v>46298</v>
+      </c>
       <c r="AB27" s="8" t="inlineStr">
         <is>
           <t>Basic</t>

--- a/willitboard_operadores.xlsx
+++ b/willitboard_operadores.xlsx
@@ -2970,7 +2970,7 @@
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>10kg Carry-on bag</t>
+          <t>10kg carry-on bag</t>
         </is>
       </c>
       <c r="N19" s="8" t="n">
@@ -2998,7 +2998,7 @@
       <c r="X19" s="8" t="n"/>
       <c r="Y19" s="8" t="inlineStr">
         <is>
-          <t>[SIN VERIFICAR] Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. Página: 'Carry-on baggage must fit inside the gauge units at the airport (including wheels and handles).' La valija de 10 kg viene en Plus, Advantage, Aer Space y socios AerClub Silver+; en la tarifa base se compra. Falta: nombre exacto de la tarifa base (¿Saver?) y del extra. La URL /prepare/bags/carry-on-baggage/ devolvió 405 a la herramienta; se leyó el modal /localized/en/modals/baggage-information.html.</t>
+          <t>Verificado por Marcos el 03/10/2026 con capturas: 10kg Carry-on Bag 55 x 40 x 24; Small Personal Item 40 x 30 x 20; 'including wheels and handles'; '(Not included in Saver fares)'; extra '10kg carry-on bag'. Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. Página: 'Carry-on baggage must fit inside the gauge units at the airport (including wheels and handles).' La valija de 10 kg viene en Plus, Advantage, Aer Space y socios AerClub Silver+; en la tarifa base se compra. Falta: nombre exacto de la tarifa base (¿Saver?) y del extra. La URL /prepare/bags/carry-on-baggage/ devolvió 405 a la herramienta; se leyó el modal /localized/en/modals/baggage-information.html. [Releído por el asistente el 03/10/2026 en el Chrome de Marcos, texto real de la página] /prepare/bags/carry-on-baggage/ ahora abre: '1 x 10kg Carry-on Bag ... Height 55cm Width 40cm Depth 24cm'; '1 x Small Personal Item ... Height 40cm Width 30cm Depth 20cm'; 'must fit inside the gauge units at the airport (including wheels and handles)'; 'you must book a "10kg carry-on bag" online from €9.99/£9.99'; incluido en 'All Plus, Advantage, AerSpace ... (Not included in Saver fares)'. Bolso sin peso.</t>
         </is>
       </c>
       <c r="Z19" s="9" t="inlineStr">
@@ -3006,8 +3006,14 @@
           <t>https://www.aerlingus.com/prepare/bags/carry-on-baggage/</t>
         </is>
       </c>
-      <c r="AA19" s="35" t="n"/>
-      <c r="AB19" s="8" t="n"/>
+      <c r="AA19" s="35" t="n">
+        <v>46298</v>
+      </c>
+      <c r="AB19" s="8" t="inlineStr">
+        <is>
+          <t>Saver</t>
+        </is>
+      </c>
       <c r="AC19" s="8" t="n"/>
     </row>
     <row r="20">
@@ -3063,7 +3069,7 @@
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t>Large hand luggage</t>
+          <t>Large cabin bag</t>
         </is>
       </c>
       <c r="N20" s="8" t="n">
@@ -3087,7 +3093,7 @@
       <c r="X20" s="8" t="n"/>
       <c r="Y20" s="8" t="inlineStr">
         <is>
-          <t>[SIN VERIFICAR] Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. Personal 40x30x25 en todas las tarifas. Valija 55x40x23 hasta 8 kg: incluida en SMART y BIZclass; en BASIC se paga (desde 18 EUR / 16 GBP según la herramienta, NO cargado). Ruedas y asas: la herramienta no encontró mención. Confirmar nombre exacto del extra.</t>
+          <t>Verificado por Marcos el 03/10/2026 con capturas: tabla 'Hand baggage per fare', Basic: Small underseat bag 40 x 30 x 25 incluido; 'Large cabin bag (8 kg) (max. 55 x 40 x 23 cm)' no incluida ('—', from €18 / £16). Ruedas y asas: no lo dice. Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. Personal 40x30x25 en todas las tarifas. Valija 55x40x23 hasta 8 kg: incluida en SMART y BIZclass; en BASIC se paga (desde 18 EUR / 16 GBP según la herramienta, NO cargado). Ruedas y asas: la herramienta no encontró mención. Confirmar nombre exacto del extra. [Releído por el asistente el 03/10/2026 en el Chrome de Marcos, texto real de la página] Tabla 'Hand baggage per fare': Basic / Smart / BIZclass. 'Small underseat bag (max. 40 x 30 x 25 cm)' Included en las tres. 'Large cabin bag (8 kg) (max. 55 x 40 x 23 cm)': Basic 'Not included', Smart y BIZclass 'Included'. El extra se llama 'Large cabin bag' en la tabla y 'Large hand luggage' más abajo; se usa el de la tabla. Ruedas y asas: no lo dice. Precio del extra no cargado (la página da dos cifras distintas: 'from €18 / £16' y 'from 21 €').</t>
         </is>
       </c>
       <c r="Z20" s="9" t="inlineStr">
@@ -3095,10 +3101,12 @@
           <t>https://www.eurowings.com/en/information/baggage/hand-baggage-policy.html</t>
         </is>
       </c>
-      <c r="AA20" s="35" t="n"/>
+      <c r="AA20" s="35" t="n">
+        <v>46298</v>
+      </c>
       <c r="AB20" s="8" t="inlineStr">
         <is>
-          <t>BASIC</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="AC20" s="8" t="n"/>
@@ -3178,7 +3186,7 @@
       <c r="X21" s="8" t="n"/>
       <c r="Y21" s="8" t="inlineStr">
         <is>
-          <t>[SIN VERIFICAR] Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. Página: 'When travelling with TAP, you can take hand baggage and a personal item free of charge.' Valija 55x40x25 / 10 kg; personal 40x30x15 / 2 kg. Confirmar que vale también para la tarifa más barata en Europa (Discount) y si las medidas incluyen ruedas y asas (la herramienta no lo encontró).</t>
+          <t>Verificado por Marcos el 03/10/2026 con capturas de /en-pt/information/baggage/hand-baggage (Hand baggage 10 kg, 55 x 40 x 25; Personal item 2 kg, 40 x 30 x 15) y de /en-pt/bookings/tap-fares (Discount: Hand baggage 1 x 10 kg). Ruedas y asas: no lo dice, queda vacío. Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. Página: 'When travelling with TAP, you can take hand baggage and a personal item free of charge.' Valija 55x40x25 / 10 kg; personal 40x30x15 / 2 kg. Confirmar que vale también para la tarifa más barata en Europa (Discount) y si las medidas incluyen ruedas y asas (la herramienta no lo encontró). [Releído por el asistente el 03/10/2026 en el Chrome de Marcos, texto real de la página] /en-pt/information/baggage/hand-baggage: 'Hand baggage Maximum weight: 10 kg ... Maximum dimensions: 55 x 40 x 25 cm (height x length x width)'; 'Personal item Maximum weight: 2 kg ... 40 x 30 x 15 cm'. Ruedas y asas: no lo dice. Tarifa más barata en Europa: página /en-pt/bookings/tap-fares, 'Flights to Europe and North Africa ... Discount Classic Plus / Hand baggage 1 x 10 kg' en las tres; 'Discount: a low price for those traveling with hand baggage only'. Ojo: esa segunda URL no cabe en fuente_url.</t>
         </is>
       </c>
       <c r="Z21" s="9" t="inlineStr">
@@ -3186,8 +3194,14 @@
           <t>https://www.flytap.com/en-pt/baggage/hand-baggage</t>
         </is>
       </c>
-      <c r="AA21" s="35" t="n"/>
-      <c r="AB21" s="8" t="n"/>
+      <c r="AA21" s="35" t="n">
+        <v>46298</v>
+      </c>
+      <c r="AB21" s="8" t="inlineStr">
+        <is>
+          <t>Discount</t>
+        </is>
+      </c>
       <c r="AC21" s="8" t="n"/>
     </row>
     <row r="22">
@@ -3267,7 +3281,7 @@
       <c r="X22" s="8" t="n"/>
       <c r="Y22" s="8" t="inlineStr">
         <is>
-          <t>[SIN VERIFICAR] Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. Página: '10kg hand luggage allowance included as standard (excluding infants) which must be no larger than 56cm x 45cm x 25cm (including wheels and handles)' y 'one small under-seat bag ... must not exceed 40 x 30 x 20cm'. Bolso sin peso publicado. Segundo caso tipo BA: todo incluido.</t>
+          <t>Verificado por Marcos el 03/10/2026 con captura de jet2.com/en/baggage (vista en español): 56 x 45 x 25 cm, 10 kg, incluido, '(incluyendo ruedas y asas)'; bolso 40 x 30 x 20 cm. Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. Página: '10kg hand luggage allowance included as standard (excluding infants) which must be no larger than 56cm x 45cm x 25cm (including wheels and handles)' y 'one small under-seat bag ... must not exceed 40 x 30 x 20cm'. Bolso sin peso publicado. Segundo caso tipo BA: todo incluido. [Releído por el asistente el 03/10/2026 en el Chrome de Marcos, texto real de la página] Texto confirmado igual. Además: 'On busy flights, we may need to ask you to put your 10kg hand luggage in the hold' (se vende 'Guaranteed Cabin Luggage'). Sin nombre de tarifa: tarifa_referencia vacía.</t>
         </is>
       </c>
       <c r="Z22" s="9" t="inlineStr">
@@ -3275,7 +3289,9 @@
           <t>https://www.jet2.com/en/baggage</t>
         </is>
       </c>
-      <c r="AA22" s="35" t="n"/>
+      <c r="AA22" s="35" t="n">
+        <v>46298</v>
+      </c>
       <c r="AB22" s="8" t="n"/>
       <c r="AC22" s="8" t="n"/>
     </row>
@@ -3332,10 +3348,10 @@
       </c>
       <c r="M23" s="8" t="n"/>
       <c r="N23" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="O23" s="8" t="n">
         <v>90</v>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>70</v>
       </c>
       <c r="P23" s="8" t="n">
         <v>50</v>
@@ -3354,7 +3370,7 @@
       <c r="X23" s="8" t="n"/>
       <c r="Y23" s="8" t="inlineStr">
         <is>
-          <t>[SIN VERIFICAR] Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. PRIMER TREN DIMENSIONAL. '2 suitcases + 1 item of hand luggage'; 'hand luggage ... maximum of 40 cm x 30 cm x 15 cm'; 'suitcase ... maximum of 70 cm x 90 cm x 50 cm'. Multa 50/100/150 EUR por bultos de más o fuera de medida (NO cargada en tarifas). Vale también para Intercités según la página. OJO ANTES DE PUBLICAR: las etiquetas del sitio dicen 'personal item' / 'cabin bag'; para un tren hay que mostrar 'hand luggage' / 'suitcase' (cambio chico en build_site y diccionarios).</t>
+          <t>CONFIRMADO por Marcos el 03/10/2026 con capturas de sncf-connect.com/en-en/help/transport-luggage; al publicar, verificado_el = 2026-10-03. Sin fecha todavía a propósito: falta adaptar las etiquetas de tren. [SIN VERIFICAR] Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. PRIMER TREN DIMENSIONAL. '2 suitcases + 1 item of hand luggage'; 'hand luggage ... maximum of 40 cm x 30 cm x 15 cm'; 'suitcase ... maximum of 70 cm x 90 cm x 50 cm'. Multa 50/100/150 EUR por bultos de más o fuera de medida (NO cargada en tarifas). Vale también para Intercités según la página. OJO ANTES DE PUBLICAR: las etiquetas del sitio dicen 'personal item' / 'cabin bag'; para un tren hay que mostrar 'hand luggage' / 'suitcase' (cambio chico en build_site y diccionarios). [Releído por el asistente el 03/10/2026 en el Chrome de Marcos, texto real de la página; sigue SIN VERIFICAR por Marcos] 'INTERCITÉS and TGV INOUI journeys in France and to Europe': '2 suitcases + 1 item of hand luggage' o '1 suitcase + 1 special item + 1 item of hand luggage'; 'hand luggage ... maximum of 40 cm x 30 cm x 15 cm'; 'suitcase ... maximum of 70 cm x 90 cm x 50 cm' (se cargó en ese orden, antes estaba 90 x 70 x 50). Sin peso. OJO: TGV INOUI/ICE en cooperación con DB tienen otra regla ('maximum dimensions of 130 x 90 cm per item').</t>
         </is>
       </c>
       <c r="Z23" s="9" t="inlineStr">
@@ -3441,7 +3457,7 @@
       <c r="X24" s="8" t="n"/>
       <c r="Y24" s="8" t="inlineStr">
         <is>
-          <t>[SIN VERIFICAR] Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. OUIGO Francia (no OUIGO España, que tiene otras reglas). 'one item of cabin luggage (55 x 35 x 25 cm)' y 'one item of hand luggage (40 x 30 x 15 cm)'. Bulto extra o voluminoso hasta 130x90x50 y 30 kg: 5 EUR al reservar, 20 EUR en el lugar (NO cargado). Confirmar que las dos piezas van incluidas en el billete básico. Misma advertencia de etiquetas que TGV INOUI.</t>
+          <t>CONFIRMADO por Marcos el 03/10/2026 con capturas de sncf-connect.com/en-en/help/transport-luggage; al publicar, verificado_el = 2026-10-03. Sin fecha todavía a propósito: falta adaptar las etiquetas de tren y mostrar 'sin límite de peso según el operador'. [SIN VERIFICAR] Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. OUIGO Francia (no OUIGO España, que tiene otras reglas). 'one item of cabin luggage (55 x 35 x 25 cm)' y 'one item of hand luggage (40 x 30 x 15 cm)'. Bulto extra o voluminoso hasta 130x90x50 y 30 kg: 5 EUR al reservar, 20 EUR en el lugar (NO cargado). Confirmar que las dos piezas van incluidas en el billete básico. Misma advertencia de etiquetas que TGV INOUI. [Releído por el asistente el 03/10/2026 en el Chrome de Marcos, texto real de la página; sigue SIN VERIFICAR por Marcos] 'Your train ticket includes one item of cabin luggage (55 x 35 x 25 cm) with no weight limit and one item of hand luggage (40 x 30 x 15 cm)'. Extra o voluminoso hasta 130 x 90 x 50 cm y 30 kg: '€5 per item' al reservar, '€20 per item' en el lugar. OJO: la fuente dice explícitamente 'no weight limit' para la maleta; hoy el sitio, con peso vacío, diría 'no hay límite de peso publicado', que no es exacto.</t>
         </is>
       </c>
       <c r="Z24" s="9" t="inlineStr">

--- a/willitboard_operadores.xlsx
+++ b/willitboard_operadores.xlsx
@@ -3860,23 +3860,75 @@
       <c r="AC28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n"/>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="8" t="n"/>
-      <c r="L29" s="8" t="n"/>
-      <c r="M29" s="8" t="n"/>
-      <c r="N29" s="8" t="n"/>
-      <c r="O29" s="8" t="n"/>
-      <c r="P29" s="8" t="n"/>
-      <c r="Q29" s="8" t="n"/>
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>aerolineas-argentinas</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Aerolíneas Argentinas</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>LATAM</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t>Carry on</t>
+        </is>
+      </c>
+      <c r="N29" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O29" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="P29" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q29" s="8" t="n">
+        <v>8</v>
+      </c>
       <c r="R29" s="8" t="n"/>
       <c r="S29" s="33" t="n"/>
       <c r="T29" s="8" t="n"/>
@@ -3884,30 +3936,96 @@
       <c r="V29" s="8" t="n"/>
       <c r="W29" s="8" t="n"/>
       <c r="X29" s="8" t="n"/>
-      <c r="Y29" s="8" t="n"/>
-      <c r="Z29" s="9" t="n"/>
-      <c r="AA29" s="35" t="n"/>
-      <c r="AB29" s="8" t="n"/>
+      <c r="Y29" s="8" t="inlineStr">
+        <is>
+          <t>Verificado por Marcos el 23/10/2026 con capturas de aerolineas.com.ar/es-eu/franquicia-de-equipaje (con VPN: el sitio devuelve 403 desde Dinamarca) y de aerolineas.com.ar/es-eu/tarifas-tu-medida. Artículo personal: 'En todos nuestros vuelos podrás llevar a bordo 1 artículo personal de hasta 3 kg sin cargo, puede ser una mochila, cartera, bolso para laptop o bolso para bebé'; dibujo con 40 cm × 30 cm × 15 cm; 'Cabotaje e internacional: peso máximo 3Kg'. Carry on: 1 pieza, dibujo con 55 cm × 35 cm × 25 cm; 'Cabotaje: peso máximo 8Kg. Internacional: peso máximo 10Kg. Sin cargo según la tarifa'. Ruedas y manijas: no lo dice; queda vacío. Tabla de tarifas (Base, Plus, Flex, Promo Premium Economy, Premium Economy; en EE. UU., México, República Dominicana y Europa además Promo Economy+, Economy+, Promo Business y Business): artículo personal 'Hasta 3 kg' en todas. Equipaje de mano con Base: 'Con cargo' en cabotaje (comprando desde Argentina y desde el exterior) y en Bolivia, Chile, Paraguay, Uruguay y Perú; '1 pieza de 10 kg' incluida en Brasil y Colombia, Aruba y Curazao, República Dominicana, México, Estados Unidos y Europa. Desde Plus: cabotaje 'Carry on: 8 kg'; Bolivia, Chile, Paraguay, Uruguay y Perú '1 pieza de 10 kg'. Referencia elegida por Marcos el 23/10/2026: Base en su caso más restrictivo (cabotaje: con cargo, 8 kg), mismo criterio que Avianca y LATAM. Consecuencia conocida: en rutas a Europa o EE. UU. la ficha dice que la valija se paga aparte, cuando con Base va incluida (10 kg). Precio del extra no cargado.</t>
+        </is>
+      </c>
+      <c r="Z29" s="9" t="inlineStr">
+        <is>
+          <t>https://www.aerolineas.com.ar/es-eu/franquicia-de-equipaje</t>
+        </is>
+      </c>
+      <c r="AA29" s="35" t="n">
+        <v>46318</v>
+      </c>
+      <c r="AB29" s="8" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
       <c r="AC29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n"/>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="n"/>
-      <c r="J30" s="8" t="n"/>
-      <c r="K30" s="8" t="n"/>
-      <c r="L30" s="8" t="n"/>
-      <c r="M30" s="8" t="n"/>
-      <c r="N30" s="8" t="n"/>
-      <c r="O30" s="8" t="n"/>
-      <c r="P30" s="8" t="n"/>
-      <c r="Q30" s="8" t="n"/>
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>flybondi</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Flybondi</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>LATAM</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>dimensional</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I30" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="K30" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>Carry-on</t>
+        </is>
+      </c>
+      <c r="N30" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="O30" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="P30" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q30" s="8" t="n">
+        <v>9</v>
+      </c>
       <c r="R30" s="8" t="n"/>
       <c r="S30" s="33" t="n"/>
       <c r="T30" s="8" t="n"/>
@@ -3915,9 +4033,19 @@
       <c r="V30" s="8" t="n"/>
       <c r="W30" s="8" t="n"/>
       <c r="X30" s="8" t="n"/>
-      <c r="Y30" s="8" t="n"/>
-      <c r="Z30" s="9" t="n"/>
-      <c r="AA30" s="35" t="n"/>
+      <c r="Y30" s="8" t="inlineStr">
+        <is>
+          <t>Verificado por Marcos el 23/10/2026 con capturas de ayuda.flybondi.com/es-419/article/117 ('¿Cuales son las medidas permitidas y límites de peso para mi equipaje de mano?'). VUELOS NACIONALES: 'Tenés incluido un equipaje de mano por pasajero (mochila,cartera o bolso) que debe medir hasta 30cmx40cmx20cm (ancho x alto x profundidad) y podrá pesar hasta 06 kg para guardar debajo del asiento delantero.' 'Adicional, podés agregar en la web, con costo, tu equipaje de cabina (Carry-on). Puede medir hasta: 35cmx55cmx25cm (ancho x alto x profundidad) y pesar un máximo de hasta 9kg (No se podrá abonar kilos extras para el equipaje de cabina.)' 'Sólo se podrá llevar un único bulto por persona.' (no aclara si limita artículo personal + carry-on juntos; el esquema no tiene campo para eso). Menores de 2 años: mochila de hasta 6 kilos con las mismas medidas. INTERNACIONALES: desde o hacia Brasil, artículo personal 30cmX40cmx20 hasta 10kg; desde o hacia Perú/Paraguay, hasta 6kg; carry-on igual en todas (35x55x25, 9 kg, con costo). Referencia elegida el 23/10/2026: caso más restrictivo (vuelos nacionales, 6 kg), mismo criterio que Aerolíneas Argentinas. La página no nombra tarifas: tarifa_referencia vacía. Ruedas y manijas: no lo dice; queda vacío. Precio del extra no cargado.</t>
+        </is>
+      </c>
+      <c r="Z30" s="9" t="inlineStr">
+        <is>
+          <t>https://ayuda.flybondi.com/es-419/article/117-cuales-son-las-medidas-permitidas-y-limites-de-peso-para-mi-equipaje-de-mano</t>
+        </is>
+      </c>
+      <c r="AA30" s="35" t="n">
+        <v>46318</v>
+      </c>
       <c r="AB30" s="8" t="n"/>
       <c r="AC30" s="8" t="n"/>
     </row>

--- a/willitboard_operadores.xlsx
+++ b/willitboard_operadores.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,18 @@
       <c r="B54" s="21" t="inlineStr">
         <is>
           <t>Columna AC, opcional. Solo cuando el operador publica UN peso para el artículo personal y la valija juntos (por ejemplo "12 kg en total"). No se reparte entre los bultos. Si además publica un peso por bulto, va en personal_kg o cabina_kg, y el conversor rechaza un peso por bulto mayor que el combinado. En la ficha se lee "X kg en total entre los dos bultos"; en el comparador, una valija sola que pesa más que el total no entra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="21" t="inlineStr">
+        <is>
+          <t>cabina_sin_limite_peso (esquema 1.5, 25/10/2026)</t>
+        </is>
+      </c>
+      <c r="B55" s="21" t="inlineStr">
+        <is>
+          <t>Columna AD, opcional. SI solo cuando la página oficial AFIRMA que la valija no tiene límite de peso (OUIGO: 'with no weight limit'). No es lo mismo que cabina_kg vacío, que significa 'no publica peso'. El conversor rechaza SI junto con cabina_kg o peso_combinado_kg. La ficha dice 'Sin límite de peso, según &lt;operador&gt;'.</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC120"/>
+  <dimension ref="A1:AD120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1189,6 +1201,7 @@
     <col width="21" customWidth="1" min="27" max="27"/>
     <col width="22" customWidth="1" min="28" max="28"/>
     <col width="18" customWidth="1" min="29" max="29"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1337,6 +1350,11 @@
           <t>peso_combinado_kg</t>
         </is>
       </c>
+      <c r="AD1" s="17" t="inlineStr">
+        <is>
+          <t>cabina_sin_limite_peso</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
@@ -1482,6 +1500,11 @@
       <c r="AC2" s="6" t="inlineStr">
         <is>
           <t>kg para artículo personal + valija JUNTOS, solo si el operador lo publica así</t>
+        </is>
+      </c>
+      <c r="AD2" s="6" t="inlineStr">
+        <is>
+          <t>SI solo si la fuente oficial AFIRMA que la valija no tiene límite de peso; vacío si no lo dice</t>
         </is>
       </c>
     </row>
@@ -1575,6 +1598,7 @@
       </c>
       <c r="AB3" s="15" t="n"/>
       <c r="AC3" s="13" t="n"/>
+      <c r="AD3" s="31" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -1674,6 +1698,7 @@
       </c>
       <c r="AB4" s="8" t="n"/>
       <c r="AC4" s="8" t="n"/>
+      <c r="AD4" s="33" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -1773,6 +1798,7 @@
       </c>
       <c r="AB5" s="8" t="n"/>
       <c r="AC5" s="8" t="n"/>
+      <c r="AD5" s="33" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="33" t="inlineStr">
@@ -1844,6 +1870,7 @@
       </c>
       <c r="AB6" s="33" t="n"/>
       <c r="AC6" s="33" t="n"/>
+      <c r="AD6" s="33" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="33" t="inlineStr">
@@ -1915,6 +1942,7 @@
       </c>
       <c r="AB7" s="33" t="n"/>
       <c r="AC7" s="33" t="n"/>
+      <c r="AD7" s="33" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="33" t="inlineStr">
@@ -1986,6 +2014,7 @@
       </c>
       <c r="AB8" s="33" t="n"/>
       <c r="AC8" s="33" t="n"/>
+      <c r="AD8" s="33" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -2077,6 +2106,7 @@
       </c>
       <c r="AB9" s="8" t="n"/>
       <c r="AC9" s="8" t="n"/>
+      <c r="AD9" s="33" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="33" t="inlineStr">
@@ -2148,6 +2178,7 @@
       </c>
       <c r="AB10" s="33" t="n"/>
       <c r="AC10" s="33" t="n"/>
+      <c r="AD10" s="33" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -2243,6 +2274,7 @@
         </is>
       </c>
       <c r="AC11" s="8" t="n"/>
+      <c r="AD11" s="33" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -2338,6 +2370,7 @@
         </is>
       </c>
       <c r="AC12" s="8" t="n"/>
+      <c r="AD12" s="33" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -2433,6 +2466,7 @@
         </is>
       </c>
       <c r="AC13" s="8" t="n"/>
+      <c r="AD13" s="33" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -2530,6 +2564,7 @@
       <c r="AC14" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AD14" s="33" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -2629,6 +2664,7 @@
       <c r="AC15" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="AD15" s="33" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -2728,6 +2764,7 @@
       <c r="AC16" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="AD16" s="33" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -2829,6 +2866,7 @@
       <c r="AC17" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AD17" s="33" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -2916,6 +2954,7 @@
       </c>
       <c r="AB18" s="8" t="n"/>
       <c r="AC18" s="8" t="n"/>
+      <c r="AD18" s="33" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -3015,6 +3054,7 @@
         </is>
       </c>
       <c r="AC19" s="8" t="n"/>
+      <c r="AD19" s="33" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -3110,6 +3150,7 @@
         </is>
       </c>
       <c r="AC20" s="8" t="n"/>
+      <c r="AD20" s="33" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -3203,6 +3244,7 @@
         </is>
       </c>
       <c r="AC21" s="8" t="n"/>
+      <c r="AD21" s="33" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -3294,6 +3336,7 @@
       </c>
       <c r="AB22" s="8" t="n"/>
       <c r="AC22" s="8" t="n"/>
+      <c r="AD22" s="33" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -3370,7 +3413,7 @@
       <c r="X23" s="8" t="n"/>
       <c r="Y23" s="8" t="inlineStr">
         <is>
-          <t>CONFIRMADO por Marcos el 03/10/2026 con capturas de sncf-connect.com/en-en/help/transport-luggage; al publicar, verificado_el = 2026-10-03. Sin fecha todavía a propósito: falta adaptar las etiquetas de tren. [SIN VERIFICAR] Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. PRIMER TREN DIMENSIONAL. '2 suitcases + 1 item of hand luggage'; 'hand luggage ... maximum of 40 cm x 30 cm x 15 cm'; 'suitcase ... maximum of 70 cm x 90 cm x 50 cm'. Multa 50/100/150 EUR por bultos de más o fuera de medida (NO cargada en tarifas). Vale también para Intercités según la página. OJO ANTES DE PUBLICAR: las etiquetas del sitio dicen 'personal item' / 'cabin bag'; para un tren hay que mostrar 'hand luggage' / 'suitcase' (cambio chico en build_site y diccionarios). [Releído por el asistente el 03/10/2026 en el Chrome de Marcos, texto real de la página; sigue SIN VERIFICAR por Marcos] 'INTERCITÉS and TGV INOUI journeys in France and to Europe': '2 suitcases + 1 item of hand luggage' o '1 suitcase + 1 special item + 1 item of hand luggage'; 'hand luggage ... maximum of 40 cm x 30 cm x 15 cm'; 'suitcase ... maximum of 70 cm x 90 cm x 50 cm' (se cargó en ese orden, antes estaba 90 x 70 x 50). Sin peso. OJO: TGV INOUI/ICE en cooperación con DB tienen otra regla ('maximum dimensions of 130 x 90 cm per item').</t>
+          <t>CONFIRMADO por Marcos el 03/10/2026 con capturas de sncf-connect.com/en-en/help/transport-luggage; al publicar, verificado_el = 2026-10-03. Fecha cargada el 25/10/2026, al publicar con etiquetas de tren (Hand luggage / Suitcase). [SIN VERIFICAR] Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. PRIMER TREN DIMENSIONAL. '2 suitcases + 1 item of hand luggage'; 'hand luggage ... maximum of 40 cm x 30 cm x 15 cm'; 'suitcase ... maximum of 70 cm x 90 cm x 50 cm'. Multa 50/100/150 EUR por bultos de más o fuera de medida (NO cargada en tarifas). Vale también para Intercités según la página. OJO ANTES DE PUBLICAR: las etiquetas del sitio dicen 'personal item' / 'cabin bag'; para un tren hay que mostrar 'hand luggage' / 'suitcase' (cambio chico en build_site y diccionarios). [Releído por el asistente el 03/10/2026 en el Chrome de Marcos, texto real de la página; sigue SIN VERIFICAR por Marcos] 'INTERCITÉS and TGV INOUI journeys in France and to Europe': '2 suitcases + 1 item of hand luggage' o '1 suitcase + 1 special item + 1 item of hand luggage'; 'hand luggage ... maximum of 40 cm x 30 cm x 15 cm'; 'suitcase ... maximum of 70 cm x 90 cm x 50 cm' (se cargó en ese orden, antes estaba 90 x 70 x 50). Sin peso. OJO: TGV INOUI/ICE en cooperación con DB tienen otra regla ('maximum dimensions of 130 x 90 cm per item').</t>
         </is>
       </c>
       <c r="Z23" s="9" t="inlineStr">
@@ -3378,9 +3421,12 @@
           <t>https://www.sncf-connect.com/en-en/help/transport-luggage</t>
         </is>
       </c>
-      <c r="AA23" s="35" t="n"/>
+      <c r="AA23" s="35" t="n">
+        <v>46298</v>
+      </c>
       <c r="AB23" s="8" t="n"/>
       <c r="AC23" s="8" t="n"/>
+      <c r="AD23" s="33" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -3457,7 +3503,7 @@
       <c r="X24" s="8" t="n"/>
       <c r="Y24" s="8" t="inlineStr">
         <is>
-          <t>CONFIRMADO por Marcos el 03/10/2026 con capturas de sncf-connect.com/en-en/help/transport-luggage; al publicar, verificado_el = 2026-10-03. Sin fecha todavía a propósito: falta adaptar las etiquetas de tren y mostrar 'sin límite de peso según el operador'. [SIN VERIFICAR] Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. OUIGO Francia (no OUIGO España, que tiene otras reglas). 'one item of cabin luggage (55 x 35 x 25 cm)' y 'one item of hand luggage (40 x 30 x 15 cm)'. Bulto extra o voluminoso hasta 130x90x50 y 30 kg: 5 EUR al reservar, 20 EUR en el lugar (NO cargado). Confirmar que las dos piezas van incluidas en el billete básico. Misma advertencia de etiquetas que TGV INOUI. [Releído por el asistente el 03/10/2026 en el Chrome de Marcos, texto real de la página; sigue SIN VERIFICAR por Marcos] 'Your train ticket includes one item of cabin luggage (55 x 35 x 25 cm) with no weight limit and one item of hand luggage (40 x 30 x 15 cm)'. Extra o voluminoso hasta 130 x 90 x 50 cm y 30 kg: '€5 per item' al reservar, '€20 per item' en el lugar. OJO: la fuente dice explícitamente 'no weight limit' para la maleta; hoy el sitio, con peso vacío, diría 'no hay límite de peso publicado', que no es exacto.</t>
+          <t>CONFIRMADO por Marcos el 03/10/2026 con capturas de sncf-connect.com/en-en/help/transport-luggage; al publicar, verificado_el = 2026-10-03. Fecha cargada el 25/10/2026, al publicar con etiquetas de tren y cabina_sin_limite_peso = SI ('with no weight limit', esquema 1.5). [SIN VERIFICAR] Candidata preparada por el asistente el 28/09/2026 leyendo la página oficial con una herramienta de resumen. Cifras a confirmar por Marcos. OUIGO Francia (no OUIGO España, que tiene otras reglas). 'one item of cabin luggage (55 x 35 x 25 cm)' y 'one item of hand luggage (40 x 30 x 15 cm)'. Bulto extra o voluminoso hasta 130x90x50 y 30 kg: 5 EUR al reservar, 20 EUR en el lugar (NO cargado). Confirmar que las dos piezas van incluidas en el billete básico. Misma advertencia de etiquetas que TGV INOUI. [Releído por el asistente el 03/10/2026 en el Chrome de Marcos, texto real de la página; sigue SIN VERIFICAR por Marcos] 'Your train ticket includes one item of cabin luggage (55 x 35 x 25 cm) with no weight limit and one item of hand luggage (40 x 30 x 15 cm)'. Extra o voluminoso hasta 130 x 90 x 50 cm y 30 kg: '€5 per item' al reservar, '€20 per item' en el lugar. OJO: la fuente dice explícitamente 'no weight limit' para la maleta; hoy el sitio, con peso vacío, diría 'no hay límite de peso publicado', que no es exacto.</t>
         </is>
       </c>
       <c r="Z24" s="9" t="inlineStr">
@@ -3465,9 +3511,16 @@
           <t>https://www.sncf-connect.com/en-en/help/transport-luggage</t>
         </is>
       </c>
-      <c r="AA24" s="35" t="n"/>
+      <c r="AA24" s="35" t="n">
+        <v>46298</v>
+      </c>
       <c r="AB24" s="8" t="n"/>
       <c r="AC24" s="8" t="n"/>
+      <c r="AD24" s="33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -3565,6 +3618,7 @@
       </c>
       <c r="AB25" s="8" t="n"/>
       <c r="AC25" s="8" t="n"/>
+      <c r="AD25" s="33" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -3662,6 +3716,7 @@
       <c r="AC26" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="AD26" s="33" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -3759,6 +3814,7 @@
         </is>
       </c>
       <c r="AC27" s="8" t="n"/>
+      <c r="AD27" s="33" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -3858,6 +3914,7 @@
         </is>
       </c>
       <c r="AC28" s="8" t="n"/>
+      <c r="AD28" s="33" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -3955,6 +4012,7 @@
         </is>
       </c>
       <c r="AC29" s="8" t="n"/>
+      <c r="AD29" s="33" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -4048,6 +4106,7 @@
       </c>
       <c r="AB30" s="8" t="n"/>
       <c r="AC30" s="8" t="n"/>
+      <c r="AD30" s="33" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
@@ -4079,6 +4138,7 @@
       <c r="AA31" s="35" t="n"/>
       <c r="AB31" s="8" t="n"/>
       <c r="AC31" s="8" t="n"/>
+      <c r="AD31" s="33" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n"/>
@@ -4110,6 +4170,7 @@
       <c r="AA32" s="35" t="n"/>
       <c r="AB32" s="8" t="n"/>
       <c r="AC32" s="8" t="n"/>
+      <c r="AD32" s="33" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
@@ -4141,6 +4202,7 @@
       <c r="AA33" s="35" t="n"/>
       <c r="AB33" s="8" t="n"/>
       <c r="AC33" s="8" t="n"/>
+      <c r="AD33" s="33" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n"/>
@@ -4172,6 +4234,7 @@
       <c r="AA34" s="35" t="n"/>
       <c r="AB34" s="8" t="n"/>
       <c r="AC34" s="8" t="n"/>
+      <c r="AD34" s="33" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
@@ -4203,6 +4266,7 @@
       <c r="AA35" s="35" t="n"/>
       <c r="AB35" s="8" t="n"/>
       <c r="AC35" s="8" t="n"/>
+      <c r="AD35" s="33" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n"/>
@@ -4234,6 +4298,7 @@
       <c r="AA36" s="35" t="n"/>
       <c r="AB36" s="8" t="n"/>
       <c r="AC36" s="8" t="n"/>
+      <c r="AD36" s="33" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
@@ -4265,6 +4330,7 @@
       <c r="AA37" s="35" t="n"/>
       <c r="AB37" s="8" t="n"/>
       <c r="AC37" s="8" t="n"/>
+      <c r="AD37" s="33" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n"/>
@@ -4296,6 +4362,7 @@
       <c r="AA38" s="35" t="n"/>
       <c r="AB38" s="8" t="n"/>
       <c r="AC38" s="8" t="n"/>
+      <c r="AD38" s="33" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
@@ -4327,6 +4394,7 @@
       <c r="AA39" s="35" t="n"/>
       <c r="AB39" s="8" t="n"/>
       <c r="AC39" s="8" t="n"/>
+      <c r="AD39" s="33" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n"/>
@@ -4358,6 +4426,7 @@
       <c r="AA40" s="35" t="n"/>
       <c r="AB40" s="8" t="n"/>
       <c r="AC40" s="8" t="n"/>
+      <c r="AD40" s="33" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
@@ -4389,6 +4458,7 @@
       <c r="AA41" s="35" t="n"/>
       <c r="AB41" s="8" t="n"/>
       <c r="AC41" s="8" t="n"/>
+      <c r="AD41" s="33" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n"/>
@@ -4420,6 +4490,7 @@
       <c r="AA42" s="35" t="n"/>
       <c r="AB42" s="8" t="n"/>
       <c r="AC42" s="8" t="n"/>
+      <c r="AD42" s="33" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n"/>
@@ -4451,6 +4522,7 @@
       <c r="AA43" s="35" t="n"/>
       <c r="AB43" s="8" t="n"/>
       <c r="AC43" s="8" t="n"/>
+      <c r="AD43" s="33" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n"/>
@@ -4482,6 +4554,7 @@
       <c r="AA44" s="35" t="n"/>
       <c r="AB44" s="8" t="n"/>
       <c r="AC44" s="8" t="n"/>
+      <c r="AD44" s="33" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n"/>
@@ -4513,6 +4586,7 @@
       <c r="AA45" s="35" t="n"/>
       <c r="AB45" s="8" t="n"/>
       <c r="AC45" s="8" t="n"/>
+      <c r="AD45" s="33" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n"/>
@@ -4544,6 +4618,7 @@
       <c r="AA46" s="35" t="n"/>
       <c r="AB46" s="8" t="n"/>
       <c r="AC46" s="8" t="n"/>
+      <c r="AD46" s="33" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n"/>
@@ -4575,6 +4650,7 @@
       <c r="AA47" s="35" t="n"/>
       <c r="AB47" s="8" t="n"/>
       <c r="AC47" s="8" t="n"/>
+      <c r="AD47" s="33" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n"/>
@@ -4606,6 +4682,7 @@
       <c r="AA48" s="35" t="n"/>
       <c r="AB48" s="8" t="n"/>
       <c r="AC48" s="8" t="n"/>
+      <c r="AD48" s="33" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
@@ -4637,6 +4714,7 @@
       <c r="AA49" s="35" t="n"/>
       <c r="AB49" s="8" t="n"/>
       <c r="AC49" s="8" t="n"/>
+      <c r="AD49" s="33" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n"/>
@@ -4668,6 +4746,7 @@
       <c r="AA50" s="35" t="n"/>
       <c r="AB50" s="8" t="n"/>
       <c r="AC50" s="8" t="n"/>
+      <c r="AD50" s="33" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n"/>
@@ -4699,6 +4778,7 @@
       <c r="AA51" s="35" t="n"/>
       <c r="AB51" s="8" t="n"/>
       <c r="AC51" s="8" t="n"/>
+      <c r="AD51" s="33" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n"/>
@@ -4730,6 +4810,7 @@
       <c r="AA52" s="35" t="n"/>
       <c r="AB52" s="8" t="n"/>
       <c r="AC52" s="8" t="n"/>
+      <c r="AD52" s="33" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
@@ -4761,6 +4842,7 @@
       <c r="AA53" s="35" t="n"/>
       <c r="AB53" s="8" t="n"/>
       <c r="AC53" s="8" t="n"/>
+      <c r="AD53" s="33" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n"/>
@@ -4792,6 +4874,7 @@
       <c r="AA54" s="35" t="n"/>
       <c r="AB54" s="8" t="n"/>
       <c r="AC54" s="8" t="n"/>
+      <c r="AD54" s="33" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
@@ -4823,6 +4906,7 @@
       <c r="AA55" s="35" t="n"/>
       <c r="AB55" s="8" t="n"/>
       <c r="AC55" s="8" t="n"/>
+      <c r="AD55" s="33" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n"/>
@@ -4854,6 +4938,7 @@
       <c r="AA56" s="35" t="n"/>
       <c r="AB56" s="8" t="n"/>
       <c r="AC56" s="8" t="n"/>
+      <c r="AD56" s="33" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
@@ -4885,6 +4970,7 @@
       <c r="AA57" s="35" t="n"/>
       <c r="AB57" s="8" t="n"/>
       <c r="AC57" s="8" t="n"/>
+      <c r="AD57" s="33" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n"/>
@@ -4916,6 +5002,7 @@
       <c r="AA58" s="35" t="n"/>
       <c r="AB58" s="8" t="n"/>
       <c r="AC58" s="8" t="n"/>
+      <c r="AD58" s="33" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
@@ -4947,6 +5034,7 @@
       <c r="AA59" s="35" t="n"/>
       <c r="AB59" s="8" t="n"/>
       <c r="AC59" s="8" t="n"/>
+      <c r="AD59" s="33" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n"/>
@@ -4978,6 +5066,7 @@
       <c r="AA60" s="35" t="n"/>
       <c r="AB60" s="8" t="n"/>
       <c r="AC60" s="8" t="n"/>
+      <c r="AD60" s="33" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
@@ -5009,6 +5098,7 @@
       <c r="AA61" s="35" t="n"/>
       <c r="AB61" s="8" t="n"/>
       <c r="AC61" s="8" t="n"/>
+      <c r="AD61" s="33" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n"/>
@@ -5040,6 +5130,7 @@
       <c r="AA62" s="35" t="n"/>
       <c r="AB62" s="8" t="n"/>
       <c r="AC62" s="8" t="n"/>
+      <c r="AD62" s="33" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n"/>
@@ -5071,6 +5162,7 @@
       <c r="AA63" s="35" t="n"/>
       <c r="AB63" s="8" t="n"/>
       <c r="AC63" s="8" t="n"/>
+      <c r="AD63" s="33" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n"/>
@@ -5102,6 +5194,7 @@
       <c r="AA64" s="35" t="n"/>
       <c r="AB64" s="8" t="n"/>
       <c r="AC64" s="8" t="n"/>
+      <c r="AD64" s="33" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n"/>
@@ -5133,6 +5226,7 @@
       <c r="AA65" s="35" t="n"/>
       <c r="AB65" s="8" t="n"/>
       <c r="AC65" s="8" t="n"/>
+      <c r="AD65" s="33" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n"/>
@@ -5164,6 +5258,7 @@
       <c r="AA66" s="35" t="n"/>
       <c r="AB66" s="8" t="n"/>
       <c r="AC66" s="8" t="n"/>
+      <c r="AD66" s="33" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n"/>
@@ -5195,6 +5290,7 @@
       <c r="AA67" s="35" t="n"/>
       <c r="AB67" s="8" t="n"/>
       <c r="AC67" s="8" t="n"/>
+      <c r="AD67" s="33" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n"/>
@@ -5226,6 +5322,7 @@
       <c r="AA68" s="35" t="n"/>
       <c r="AB68" s="8" t="n"/>
       <c r="AC68" s="8" t="n"/>
+      <c r="AD68" s="33" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
@@ -5257,6 +5354,7 @@
       <c r="AA69" s="35" t="n"/>
       <c r="AB69" s="8" t="n"/>
       <c r="AC69" s="8" t="n"/>
+      <c r="AD69" s="33" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n"/>
@@ -5288,6 +5386,7 @@
       <c r="AA70" s="35" t="n"/>
       <c r="AB70" s="8" t="n"/>
       <c r="AC70" s="8" t="n"/>
+      <c r="AD70" s="33" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
@@ -5319,6 +5418,7 @@
       <c r="AA71" s="35" t="n"/>
       <c r="AB71" s="8" t="n"/>
       <c r="AC71" s="8" t="n"/>
+      <c r="AD71" s="33" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n"/>
@@ -5350,6 +5450,7 @@
       <c r="AA72" s="35" t="n"/>
       <c r="AB72" s="8" t="n"/>
       <c r="AC72" s="8" t="n"/>
+      <c r="AD72" s="33" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
@@ -5381,6 +5482,7 @@
       <c r="AA73" s="35" t="n"/>
       <c r="AB73" s="8" t="n"/>
       <c r="AC73" s="8" t="n"/>
+      <c r="AD73" s="33" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n"/>
@@ -5412,6 +5514,7 @@
       <c r="AA74" s="35" t="n"/>
       <c r="AB74" s="8" t="n"/>
       <c r="AC74" s="8" t="n"/>
+      <c r="AD74" s="33" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n"/>
@@ -5443,6 +5546,7 @@
       <c r="AA75" s="35" t="n"/>
       <c r="AB75" s="8" t="n"/>
       <c r="AC75" s="8" t="n"/>
+      <c r="AD75" s="33" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="n"/>
@@ -5474,6 +5578,7 @@
       <c r="AA76" s="35" t="n"/>
       <c r="AB76" s="8" t="n"/>
       <c r="AC76" s="8" t="n"/>
+      <c r="AD76" s="33" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n"/>
@@ -5505,6 +5610,7 @@
       <c r="AA77" s="35" t="n"/>
       <c r="AB77" s="8" t="n"/>
       <c r="AC77" s="8" t="n"/>
+      <c r="AD77" s="33" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n"/>
@@ -5536,6 +5642,7 @@
       <c r="AA78" s="35" t="n"/>
       <c r="AB78" s="8" t="n"/>
       <c r="AC78" s="8" t="n"/>
+      <c r="AD78" s="33" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n"/>
@@ -5567,6 +5674,7 @@
       <c r="AA79" s="35" t="n"/>
       <c r="AB79" s="8" t="n"/>
       <c r="AC79" s="8" t="n"/>
+      <c r="AD79" s="33" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n"/>
@@ -5598,6 +5706,7 @@
       <c r="AA80" s="35" t="n"/>
       <c r="AB80" s="8" t="n"/>
       <c r="AC80" s="8" t="n"/>
+      <c r="AD80" s="33" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n"/>
@@ -5629,6 +5738,7 @@
       <c r="AA81" s="35" t="n"/>
       <c r="AB81" s="8" t="n"/>
       <c r="AC81" s="8" t="n"/>
+      <c r="AD81" s="33" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="8" t="n"/>
@@ -5660,6 +5770,7 @@
       <c r="AA82" s="35" t="n"/>
       <c r="AB82" s="8" t="n"/>
       <c r="AC82" s="8" t="n"/>
+      <c r="AD82" s="33" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n"/>
@@ -5691,6 +5802,7 @@
       <c r="AA83" s="35" t="n"/>
       <c r="AB83" s="8" t="n"/>
       <c r="AC83" s="8" t="n"/>
+      <c r="AD83" s="33" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="8" t="n"/>
@@ -5722,6 +5834,7 @@
       <c r="AA84" s="35" t="n"/>
       <c r="AB84" s="8" t="n"/>
       <c r="AC84" s="8" t="n"/>
+      <c r="AD84" s="33" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n"/>
@@ -5753,6 +5866,7 @@
       <c r="AA85" s="35" t="n"/>
       <c r="AB85" s="8" t="n"/>
       <c r="AC85" s="8" t="n"/>
+      <c r="AD85" s="33" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="8" t="n"/>
@@ -5784,6 +5898,7 @@
       <c r="AA86" s="35" t="n"/>
       <c r="AB86" s="8" t="n"/>
       <c r="AC86" s="8" t="n"/>
+      <c r="AD86" s="33" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n"/>
@@ -5815,6 +5930,7 @@
       <c r="AA87" s="35" t="n"/>
       <c r="AB87" s="8" t="n"/>
       <c r="AC87" s="8" t="n"/>
+      <c r="AD87" s="33" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="8" t="n"/>
@@ -5846,6 +5962,7 @@
       <c r="AA88" s="35" t="n"/>
       <c r="AB88" s="8" t="n"/>
       <c r="AC88" s="8" t="n"/>
+      <c r="AD88" s="33" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n"/>
@@ -5877,6 +5994,7 @@
       <c r="AA89" s="35" t="n"/>
       <c r="AB89" s="8" t="n"/>
       <c r="AC89" s="8" t="n"/>
+      <c r="AD89" s="33" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="8" t="n"/>
@@ -5908,6 +6026,7 @@
       <c r="AA90" s="35" t="n"/>
       <c r="AB90" s="8" t="n"/>
       <c r="AC90" s="8" t="n"/>
+      <c r="AD90" s="33" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n"/>
@@ -5939,6 +6058,7 @@
       <c r="AA91" s="35" t="n"/>
       <c r="AB91" s="8" t="n"/>
       <c r="AC91" s="8" t="n"/>
+      <c r="AD91" s="33" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="8" t="n"/>
@@ -5970,6 +6090,7 @@
       <c r="AA92" s="35" t="n"/>
       <c r="AB92" s="8" t="n"/>
       <c r="AC92" s="8" t="n"/>
+      <c r="AD92" s="33" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n"/>
@@ -6001,6 +6122,7 @@
       <c r="AA93" s="35" t="n"/>
       <c r="AB93" s="8" t="n"/>
       <c r="AC93" s="8" t="n"/>
+      <c r="AD93" s="33" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="8" t="n"/>
@@ -6032,6 +6154,7 @@
       <c r="AA94" s="35" t="n"/>
       <c r="AB94" s="8" t="n"/>
       <c r="AC94" s="8" t="n"/>
+      <c r="AD94" s="33" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n"/>
@@ -6063,6 +6186,7 @@
       <c r="AA95" s="35" t="n"/>
       <c r="AB95" s="8" t="n"/>
       <c r="AC95" s="8" t="n"/>
+      <c r="AD95" s="33" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="n"/>
@@ -6094,6 +6218,7 @@
       <c r="AA96" s="35" t="n"/>
       <c r="AB96" s="8" t="n"/>
       <c r="AC96" s="8" t="n"/>
+      <c r="AD96" s="33" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n"/>
@@ -6125,6 +6250,7 @@
       <c r="AA97" s="35" t="n"/>
       <c r="AB97" s="8" t="n"/>
       <c r="AC97" s="8" t="n"/>
+      <c r="AD97" s="33" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="8" t="n"/>
@@ -6156,6 +6282,7 @@
       <c r="AA98" s="35" t="n"/>
       <c r="AB98" s="8" t="n"/>
       <c r="AC98" s="8" t="n"/>
+      <c r="AD98" s="33" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n"/>
@@ -6187,6 +6314,7 @@
       <c r="AA99" s="35" t="n"/>
       <c r="AB99" s="8" t="n"/>
       <c r="AC99" s="8" t="n"/>
+      <c r="AD99" s="33" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="8" t="n"/>
@@ -6218,6 +6346,7 @@
       <c r="AA100" s="35" t="n"/>
       <c r="AB100" s="8" t="n"/>
       <c r="AC100" s="8" t="n"/>
+      <c r="AD100" s="33" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n"/>
@@ -6249,6 +6378,7 @@
       <c r="AA101" s="35" t="n"/>
       <c r="AB101" s="8" t="n"/>
       <c r="AC101" s="8" t="n"/>
+      <c r="AD101" s="33" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="8" t="n"/>
@@ -6280,6 +6410,7 @@
       <c r="AA102" s="35" t="n"/>
       <c r="AB102" s="8" t="n"/>
       <c r="AC102" s="8" t="n"/>
+      <c r="AD102" s="33" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="n"/>
@@ -6311,6 +6442,7 @@
       <c r="AA103" s="35" t="n"/>
       <c r="AB103" s="8" t="n"/>
       <c r="AC103" s="8" t="n"/>
+      <c r="AD103" s="33" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="8" t="n"/>
@@ -6342,6 +6474,7 @@
       <c r="AA104" s="35" t="n"/>
       <c r="AB104" s="8" t="n"/>
       <c r="AC104" s="8" t="n"/>
+      <c r="AD104" s="33" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="n"/>
@@ -6373,6 +6506,7 @@
       <c r="AA105" s="35" t="n"/>
       <c r="AB105" s="8" t="n"/>
       <c r="AC105" s="8" t="n"/>
+      <c r="AD105" s="33" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="8" t="n"/>
@@ -6404,6 +6538,7 @@
       <c r="AA106" s="35" t="n"/>
       <c r="AB106" s="8" t="n"/>
       <c r="AC106" s="8" t="n"/>
+      <c r="AD106" s="33" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="n"/>
@@ -6435,6 +6570,7 @@
       <c r="AA107" s="35" t="n"/>
       <c r="AB107" s="8" t="n"/>
       <c r="AC107" s="8" t="n"/>
+      <c r="AD107" s="33" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="8" t="n"/>
@@ -6466,6 +6602,7 @@
       <c r="AA108" s="35" t="n"/>
       <c r="AB108" s="8" t="n"/>
       <c r="AC108" s="8" t="n"/>
+      <c r="AD108" s="33" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="n"/>
@@ -6497,6 +6634,7 @@
       <c r="AA109" s="35" t="n"/>
       <c r="AB109" s="8" t="n"/>
       <c r="AC109" s="8" t="n"/>
+      <c r="AD109" s="33" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="8" t="n"/>
@@ -6528,6 +6666,7 @@
       <c r="AA110" s="35" t="n"/>
       <c r="AB110" s="8" t="n"/>
       <c r="AC110" s="8" t="n"/>
+      <c r="AD110" s="33" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="n"/>
@@ -6559,6 +6698,7 @@
       <c r="AA111" s="35" t="n"/>
       <c r="AB111" s="8" t="n"/>
       <c r="AC111" s="8" t="n"/>
+      <c r="AD111" s="33" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="8" t="n"/>
@@ -6590,6 +6730,7 @@
       <c r="AA112" s="35" t="n"/>
       <c r="AB112" s="8" t="n"/>
       <c r="AC112" s="8" t="n"/>
+      <c r="AD112" s="33" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="n"/>
@@ -6621,6 +6762,7 @@
       <c r="AA113" s="35" t="n"/>
       <c r="AB113" s="8" t="n"/>
       <c r="AC113" s="8" t="n"/>
+      <c r="AD113" s="33" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="8" t="n"/>
@@ -6652,6 +6794,7 @@
       <c r="AA114" s="35" t="n"/>
       <c r="AB114" s="8" t="n"/>
       <c r="AC114" s="8" t="n"/>
+      <c r="AD114" s="33" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="n"/>
@@ -6683,6 +6826,7 @@
       <c r="AA115" s="35" t="n"/>
       <c r="AB115" s="8" t="n"/>
       <c r="AC115" s="8" t="n"/>
+      <c r="AD115" s="33" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="8" t="n"/>
@@ -6714,6 +6858,7 @@
       <c r="AA116" s="35" t="n"/>
       <c r="AB116" s="8" t="n"/>
       <c r="AC116" s="8" t="n"/>
+      <c r="AD116" s="33" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="n"/>
@@ -6745,6 +6890,7 @@
       <c r="AA117" s="35" t="n"/>
       <c r="AB117" s="8" t="n"/>
       <c r="AC117" s="8" t="n"/>
+      <c r="AD117" s="33" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="8" t="n"/>
@@ -6776,6 +6922,7 @@
       <c r="AA118" s="35" t="n"/>
       <c r="AB118" s="8" t="n"/>
       <c r="AC118" s="8" t="n"/>
+      <c r="AD118" s="33" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="n"/>
@@ -6807,6 +6954,7 @@
       <c r="AA119" s="35" t="n"/>
       <c r="AB119" s="8" t="n"/>
       <c r="AC119" s="8" t="n"/>
+      <c r="AD119" s="33" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="8" t="n"/>
@@ -6838,6 +6986,7 @@
       <c r="AA120" s="35" t="n"/>
       <c r="AB120" s="8" t="n"/>
       <c r="AC120" s="8" t="n"/>
+      <c r="AD120" s="33" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="AB3:AB120">
@@ -6845,7 +6994,7 @@
       <formula>AND($A3&lt;&gt;"",$AB3="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="18">
+  <dataValidations count="19">
     <dataValidation sqref="C3:C120" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Revisá el dato" error="Elegí una opción de la lista o dejá vacío si todavía no tenés el dato." type="list">
       <formula1>"air,rail,ferry"</formula1>
     </dataValidation>
@@ -6900,6 +7049,9 @@
     <dataValidation sqref="S3:S120" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Revisá el dato" error="Usá un número igual o mayor que cero en cm. Un dato desconocido queda vacío." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
+    <dataValidation sqref="AD3:AD120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"SI,NO"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/willitboard_operadores.xlsx
+++ b/willitboard_operadores.xlsx
@@ -4109,35 +4109,75 @@
       <c r="AD30" s="33" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n"/>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="n"/>
-      <c r="J31" s="8" t="n"/>
-      <c r="K31" s="8" t="n"/>
-      <c r="L31" s="8" t="n"/>
-      <c r="M31" s="8" t="n"/>
-      <c r="N31" s="8" t="n"/>
-      <c r="O31" s="8" t="n"/>
-      <c r="P31" s="8" t="n"/>
-      <c r="Q31" s="8" t="n"/>
-      <c r="R31" s="8" t="n"/>
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>renfe</t>
+        </is>
+      </c>
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>Renfe</t>
+        </is>
+      </c>
+      <c r="C31" s="33" t="inlineStr">
+        <is>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="D31" s="33" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E31" s="33" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F31" s="33" t="inlineStr">
+        <is>
+          <t>descriptivo</t>
+        </is>
+      </c>
+      <c r="G31" s="33" t="n"/>
+      <c r="H31" s="33" t="n"/>
+      <c r="I31" s="33" t="n"/>
+      <c r="J31" s="33" t="n"/>
+      <c r="K31" s="33" t="n"/>
+      <c r="L31" s="33" t="n"/>
+      <c r="M31" s="33" t="n"/>
+      <c r="N31" s="33" t="n"/>
+      <c r="O31" s="33" t="n"/>
+      <c r="P31" s="33" t="n"/>
+      <c r="Q31" s="33" t="n"/>
+      <c r="R31" s="33" t="n"/>
       <c r="S31" s="33" t="n"/>
-      <c r="T31" s="8" t="n"/>
-      <c r="U31" s="8" t="n"/>
-      <c r="V31" s="8" t="n"/>
-      <c r="W31" s="8" t="n"/>
-      <c r="X31" s="8" t="n"/>
-      <c r="Y31" s="8" t="n"/>
-      <c r="Z31" s="9" t="n"/>
-      <c r="AA31" s="35" t="n"/>
-      <c r="AB31" s="8" t="n"/>
-      <c r="AC31" s="8" t="n"/>
+      <c r="T31" s="33" t="n"/>
+      <c r="U31" s="33" t="n"/>
+      <c r="V31" s="33" t="n"/>
+      <c r="W31" s="33" t="inlineStr">
+        <is>
+          <t>Puedes subir a bordo del tren hasta 3 bultos considerados equipaje de mano, siempre que la suma de los tres no exceda los 25 kg de peso ni los 290 cm. de tamaño. Las dimensiones máximas permitidas son 85x55x35 cm. (alto–ancho–fondo). En el caso de viajar en el AVE Internacional entre España y Francia el equipaje de mano tiene las mismas condiciones, salvo que el etiquetaje del equipaje es obligatorio. Recuerda que para viajar en trenes Avlo la política de equipajes es más restrictiva. ¿Qué consideramos equipaje de mano? Maletas, bolsos de mano, mochilas, maletines portaordenadores y similares. Sillas y coches portabebés, siempre que vayan plegados. Además, instrumentos musicales, transportados en su funda, que no superen las dimensiones 30x120x38 cm. (ancho-largo-fondo). Todas las bicicletas y patinetes plegados dentro de una funda se consideran equipaje de mano siempre que sus dimensiones no sumen entre las tres más de 180 cm. y por tanto serán admitidas sin coste en todos los servicios regulares de Renfe Viajeros. La política de transporte de bicicletas y patinetes sin plegar depende del tipo de tren en el que viajes. Equipaje en trenes Avlo: Recuerda que, para tu viaje en Avlo, puedes llevar el siguiente equipaje incluido en el precio de tu billete: 1 equipaje de mano (bolso, mochila, etc.) de dimensiones máximas: 36x27x25 cm, sin límite de peso. 1 maleta de cabina de dimensiones máximas: 55x35x25 cm, sin límite de peso. Si necesitas añadir 1 equipaje adicional de dimensiones más grandes (maleta, bicicleta, patinete, etc.), con un máximo de 85x60x35 cm. (o que no exceda los 180 cm. en total), puedes hacerlo en el momento de la compra de tu billete por 10 € o con posterioridad a la compra de tu billete y hasta 30 minutos antes de la salida del tren en cualquiera de nuestros canales de venta por 15 €.</t>
+        </is>
+      </c>
+      <c r="X31" s="33" t="n"/>
+      <c r="Y31" s="33" t="inlineStr">
+        <is>
+          <t>VERIFICADO por Marcos el 27/10/2026: pegó el texto literal de la página oficial (secciones 'Equipaje de mano', '¿Qué consideramos equipaje de mano?' y 'Equipaje en trenes Avlo') y mandó capturas de las ilustraciones ('Medidas máx. tres bultos 290cm 25Kg' / 'Medidas máx. maleta más grande 85x55x35cm' / instrumentos 30x120x38cm). limit_type = descriptivo por decisión de Marcos (27/10/2026), como Eurostar: la regla es de varios bultos (hasta 3; 290 cm y 25 kg SUMANDO los tres; 85x55x35 cm como máximo) y el esquema no tiene dónde poner la suma de 290 cm ni un peso para 3 bultos (peso_combinado_kg es para 2). regla_texto_es = texto literal; solo se unieron las viñetas en frases con punto, se agregó 'Equipaje en trenes Avlo:' como encabezado en línea y se quitaron los textos de enlace ('Consulta toda la información'). Sin traducir. La página no nombra Larga Distancia, Media Distancia ni Cercanías; la regla habla de 'bordo del tren' sin distinguir servicios, salvo AVE Internacional (etiquetado obligatorio) y Avlo (más restrictiva). No dice si las medidas incluyen ruedas y asas. Avlo encaja como operador dimensional aparte (36x27x25 + 55x35x25 incluidos, sin límite de peso; adicional 85x60x35 o 180 cm por 10/15 EUR): candidato siguiente.</t>
+        </is>
+      </c>
+      <c r="Z31" s="36" t="inlineStr">
+        <is>
+          <t>https://www.renfe.com/es/es/viajar/informacion-util/equipajes</t>
+        </is>
+      </c>
+      <c r="AA31" s="34" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB31" s="33" t="n"/>
+      <c r="AC31" s="33" t="n"/>
       <c r="AD31" s="33" t="n"/>
     </row>
     <row r="32">

--- a/willitboard_operadores.xlsx
+++ b/willitboard_operadores.xlsx
@@ -1169,7 +1169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD120"/>
+  <dimension ref="A1:AD121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="Y10" s="33" t="inlineStr">
         <is>
-          <t>Verificado por Marcos el 23/09/2026: pegó el texto completo de la página oficial y confirmó los cuatro puntos pedidos. PRIMER FERRY DEL DATASET. limit_type = descriptivo A PROPÓSITO, mismo criterio que Eurostar: la única medida publicada, 60 x 50 x 40 cm, aplica SOLO a pasajeros a pie hacia Irlanda y hacia el Reino Unido desde Irlanda. En las rutas a Suecia, Dinamarca, Alemania, Letonia y Polonia no hay límite de tamaño, y en Harwich-Hook of Holland tampoco. Cargar 60x50x40 en la terna de cabina la aplicaría a todas las rutas y sería falso en la mayoría. Por eso la cifra vive dentro de la regla, acotada a sus rutas. Sin ningún peso en kg publicado (confirmado). La regla es TEXTUAL: frases copiadas de la página, sin parafrasear. EXCLUIDO a propósito: el párrafo final sobre productos restringidos entre el Reino Unido y la UE, porque es una regla aduanera y no de tamaño de equipaje. FUENTE: el mismo texto figura en stenaline.co.uk y en stenalinetravel.com; se cita .co.uk por ser el sitio del propio operador. pais = SE por Stena Line AB (Gotemburgo).</t>
+          <t>Verificado por Marcos el 23/09/2026: pegó el texto completo de la página oficial y confirmó los cuatro puntos pedidos. PRIMER FERRY DEL DATASET. limit_type = descriptivo A PROPÓSITO, mismo criterio que Eurostar: la única medida publicada, 60 x 50 x 40 cm, aplica SOLO a pasajeros a pie hacia Irlanda y hacia el Reino Unido desde Irlanda. En las rutas a Suecia, Dinamarca, Alemania, Letonia y Polonia no hay límite de tamaño, y en Harwich-Hook of Holland tampoco. Cargar 60x50x40 en la terna de cabina la aplicaría a todas las rutas y sería falso en la mayoría. Por eso la cifra vive dentro de la regla, acotada a sus rutas. Sin ningún peso en kg publicado (confirmado). La regla es TEXTUAL: frases copiadas de la página, sin parafrasear. EXCLUIDO a propósito: el párrafo final sobre productos restringidos entre el Reino Unido y la UE, porque es una regla aduanera y no de tamaño de equipaje. FUENTE: el mismo texto figura en stenaline.co.uk y en stenalinetravel.com; se cita .co.uk por ser el sitio del propio operador. pais = SE por Stena Line AB (Gotemburgo). Reverificado por Marcos el 31/10/2026 (captura de stenaline.co.uk, texto idéntico). stenalinetravel.com/ferry-to-holland/luggage-allowance da 404 desde esa fecha.</t>
         </is>
       </c>
       <c r="Z10" s="36" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="AA10" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="AB10" s="33" t="n"/>
@@ -4181,12 +4181,36 @@
       <c r="AD31" s="33" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n"/>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="n"/>
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>dfds</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>DFDS</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>ferry</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>descriptivo</t>
+        </is>
+      </c>
       <c r="G32" s="8" t="n"/>
       <c r="H32" s="8" t="n"/>
       <c r="I32" s="8" t="n"/>
@@ -4204,10 +4228,26 @@
       <c r="U32" s="8" t="n"/>
       <c r="V32" s="8" t="n"/>
       <c r="W32" s="8" t="n"/>
-      <c r="X32" s="8" t="n"/>
-      <c r="Y32" s="8" t="n"/>
-      <c r="Z32" s="9" t="n"/>
-      <c r="AA32" s="35" t="n"/>
+      <c r="X32" s="8" t="inlineStr">
+        <is>
+          <t>There is no weight limit of your baggage when travelling by ferry with DFDS. For the safety of yourself, other passengers, and our crew you must be able to handle and carry your luggage independently.</t>
+        </is>
+      </c>
+      <c r="Y32" s="8" t="inlineStr">
+        <is>
+          <t>Verificado por Marcos el 31/10/2026: abrió la fuente y pegó el texto. Texto pegado por Marcos desde el FAQ oficial de Newcastle-Amsterdam ("What is the baggage allowance?"). limit_type = descriptivo: DFDS no publica medidas ni kg. El asistente leyó en el navegador (no cuenta como verificación) las respuestas de Jersey ("personal belongings only and not for commercial use", sin cifras) y Estrecho de Gibraltar ("clothing and personal belongings", sin cifras). Los 50 kg y 25 kg (Jersey) que dan Ferryhopper/Ferryscanner NO figuran en las páginas oficiales leídas: no cargar. [SIN VERIFICAR, Wikipedia] Copenhague-Oslo vendida a Gotlandsbolaget a fines de 2024. pais = DK por DFDS A/S (Copenhague).</t>
+        </is>
+      </c>
+      <c r="Z32" s="9" t="inlineStr">
+        <is>
+          <t>https://www.dfds.com/en/passenger-ferries/customer-service/faqs/amsterdam-newcastle</t>
+        </is>
+      </c>
+      <c r="AA32" s="35" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
       <c r="AB32" s="8" t="n"/>
       <c r="AC32" s="8" t="n"/>
       <c r="AD32" s="33" t="n"/>
@@ -7027,6 +7067,38 @@
       <c r="AB120" s="8" t="n"/>
       <c r="AC120" s="8" t="n"/>
       <c r="AD120" s="33" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="33" t="n"/>
+      <c r="B121" s="33" t="n"/>
+      <c r="C121" s="33" t="n"/>
+      <c r="D121" s="33" t="n"/>
+      <c r="E121" s="33" t="n"/>
+      <c r="F121" s="33" t="n"/>
+      <c r="G121" s="33" t="n"/>
+      <c r="H121" s="33" t="n"/>
+      <c r="I121" s="33" t="n"/>
+      <c r="J121" s="33" t="n"/>
+      <c r="K121" s="33" t="n"/>
+      <c r="L121" s="33" t="n"/>
+      <c r="M121" s="33" t="n"/>
+      <c r="N121" s="33" t="n"/>
+      <c r="O121" s="33" t="n"/>
+      <c r="P121" s="33" t="n"/>
+      <c r="Q121" s="33" t="n"/>
+      <c r="R121" s="33" t="n"/>
+      <c r="S121" s="33" t="n"/>
+      <c r="T121" s="33" t="n"/>
+      <c r="U121" s="33" t="n"/>
+      <c r="V121" s="33" t="n"/>
+      <c r="W121" s="33" t="n"/>
+      <c r="X121" s="33" t="n"/>
+      <c r="Y121" s="33" t="n"/>
+      <c r="Z121" s="36" t="n"/>
+      <c r="AA121" s="34" t="n"/>
+      <c r="AB121" s="33" t="n"/>
+      <c r="AC121" s="33" t="n"/>
+      <c r="AD121" s="33" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="AB3:AB120">
